--- a/Pyhton Programs.xlsx
+++ b/Pyhton Programs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workplace\Python-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6AF22274-D932-4CF1-83E3-0410A23B30F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B52A7C0-0E96-4BCC-8E62-A66D45A4730A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
+    <workbookView xWindow="0" yWindow="12" windowWidth="23256" windowHeight="13176" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,11 +35,150 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="40">
+  <si>
+    <t>Program NO</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Program 1</t>
+  </si>
+  <si>
+    <t>Program 2</t>
+  </si>
+  <si>
+    <t>Program 3</t>
+  </si>
+  <si>
+    <t>Program 4</t>
+  </si>
+  <si>
+    <t>Program 5</t>
+  </si>
+  <si>
+    <t>Program 6</t>
+  </si>
+  <si>
+    <t>Program 7</t>
+  </si>
+  <si>
+    <t>Program 8</t>
+  </si>
+  <si>
+    <t>Program 9</t>
+  </si>
+  <si>
+    <t>Program 10</t>
+  </si>
+  <si>
+    <t>Program 11</t>
+  </si>
+  <si>
+    <t>Program 12</t>
+  </si>
+  <si>
+    <t>Program 13</t>
+  </si>
+  <si>
+    <t>Program 14</t>
+  </si>
+  <si>
+    <t>Program 15</t>
+  </si>
+  <si>
+    <t>Program 16</t>
+  </si>
+  <si>
+    <t>Program 17</t>
+  </si>
+  <si>
+    <t>Program 18</t>
+  </si>
+  <si>
+    <t>Program 19</t>
+  </si>
+  <si>
+    <t>Program 20</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>Print Inbuilt method</t>
+  </si>
+  <si>
+    <t>Address And Refrence comprsion</t>
+  </si>
+  <si>
+    <t>program</t>
+  </si>
+  <si>
+    <t>String Inbuilt Method</t>
+  </si>
+  <si>
+    <t>Integer in python</t>
+  </si>
+  <si>
+    <t>Boolean datatypes</t>
+  </si>
+  <si>
+    <t>Selction If and else Keyword</t>
+  </si>
+  <si>
+    <t>Greatest of Three Number Selection</t>
+  </si>
+  <si>
+    <t>Range built in funation Range(start, end, step)</t>
+  </si>
+  <si>
+    <t>Iteration in python using for loop {for &lt;variable&gt; in &lt;sequence&gt;:}</t>
+  </si>
+  <si>
+    <t>List (Array) in Python [Size of Empty list is 56 Bytes] And List built in function</t>
+  </si>
+  <si>
+    <t>Continue and Break statement is used only on loop</t>
+  </si>
+  <si>
+    <t>While loop in Pyhton used when number of iteration are not known</t>
+  </si>
+  <si>
+    <t>Nested loop usong LOOP inside LOOP</t>
+  </si>
+  <si>
+    <t>Pass Statement is uses to implements the stubs</t>
+  </si>
+  <si>
+    <t>List remove and pop confusion Removes removes first presence of element And pop Removes element from last</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -66,8 +205,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,9 +547,240 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19D1B62-8AB4-4DE6-A4B9-DCFE9C1F8102}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="92.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Pyhton Programs.xlsx
+++ b/Pyhton Programs.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workplace\Python-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B52A7C0-0E96-4BCC-8E62-A66D45A4730A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8567D43E-B80F-4632-97DD-31C956B9E70F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="12" windowWidth="23256" windowHeight="13176" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Python" sheetId="1" r:id="rId1"/>
+    <sheet name="JavaScript" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="391">
   <si>
     <t>Program NO</t>
   </si>
@@ -156,6 +157,1059 @@
   </si>
   <si>
     <t>List remove and pop confusion Removes removes first presence of element And pop Removes element from last</t>
+  </si>
+  <si>
+    <t>Tuple in Python</t>
+  </si>
+  <si>
+    <t>Program</t>
+  </si>
+  <si>
+    <t>Program1</t>
+  </si>
+  <si>
+    <t>Program2</t>
+  </si>
+  <si>
+    <t>Program3</t>
+  </si>
+  <si>
+    <t>Program4</t>
+  </si>
+  <si>
+    <t>Program5</t>
+  </si>
+  <si>
+    <t>Program6</t>
+  </si>
+  <si>
+    <t>Program7</t>
+  </si>
+  <si>
+    <t>Program8</t>
+  </si>
+  <si>
+    <t>Program9</t>
+  </si>
+  <si>
+    <t>Program10</t>
+  </si>
+  <si>
+    <t>Program11</t>
+  </si>
+  <si>
+    <t>Program12</t>
+  </si>
+  <si>
+    <t>Program13</t>
+  </si>
+  <si>
+    <t>Program14</t>
+  </si>
+  <si>
+    <t>Program15</t>
+  </si>
+  <si>
+    <t>Program16</t>
+  </si>
+  <si>
+    <t>Program17</t>
+  </si>
+  <si>
+    <t>Program18</t>
+  </si>
+  <si>
+    <t>Program19</t>
+  </si>
+  <si>
+    <t>Program20</t>
+  </si>
+  <si>
+    <t>Program21</t>
+  </si>
+  <si>
+    <t>Program22</t>
+  </si>
+  <si>
+    <t>Program23</t>
+  </si>
+  <si>
+    <t>Program24</t>
+  </si>
+  <si>
+    <t>Program25</t>
+  </si>
+  <si>
+    <t>Program26</t>
+  </si>
+  <si>
+    <t>Program27</t>
+  </si>
+  <si>
+    <t>Program28</t>
+  </si>
+  <si>
+    <t>Program29</t>
+  </si>
+  <si>
+    <t>Program30</t>
+  </si>
+  <si>
+    <t>Program31</t>
+  </si>
+  <si>
+    <t>Program32</t>
+  </si>
+  <si>
+    <t>Program33</t>
+  </si>
+  <si>
+    <t>Program34</t>
+  </si>
+  <si>
+    <t>Program35</t>
+  </si>
+  <si>
+    <t>Program36</t>
+  </si>
+  <si>
+    <t>Program37</t>
+  </si>
+  <si>
+    <t>Program38</t>
+  </si>
+  <si>
+    <t>Program39</t>
+  </si>
+  <si>
+    <t>Program40</t>
+  </si>
+  <si>
+    <t>Program41</t>
+  </si>
+  <si>
+    <t>Program42</t>
+  </si>
+  <si>
+    <t>Program43</t>
+  </si>
+  <si>
+    <t>Program44</t>
+  </si>
+  <si>
+    <t>Program45</t>
+  </si>
+  <si>
+    <t>Program46</t>
+  </si>
+  <si>
+    <t>Program47</t>
+  </si>
+  <si>
+    <t>Program48</t>
+  </si>
+  <si>
+    <t>Program49</t>
+  </si>
+  <si>
+    <t>Program50</t>
+  </si>
+  <si>
+    <t>Program51</t>
+  </si>
+  <si>
+    <t>Program52</t>
+  </si>
+  <si>
+    <t>Program53</t>
+  </si>
+  <si>
+    <t>Program54</t>
+  </si>
+  <si>
+    <t>Program55</t>
+  </si>
+  <si>
+    <t>Program56</t>
+  </si>
+  <si>
+    <t>Program57</t>
+  </si>
+  <si>
+    <t>Program58</t>
+  </si>
+  <si>
+    <t>Program59</t>
+  </si>
+  <si>
+    <t>Program60</t>
+  </si>
+  <si>
+    <t>Program61</t>
+  </si>
+  <si>
+    <t>Program62</t>
+  </si>
+  <si>
+    <t>Program63</t>
+  </si>
+  <si>
+    <t>Program64</t>
+  </si>
+  <si>
+    <t>Program65</t>
+  </si>
+  <si>
+    <t>Program66</t>
+  </si>
+  <si>
+    <t>Program67</t>
+  </si>
+  <si>
+    <t>Program68</t>
+  </si>
+  <si>
+    <t>Program69</t>
+  </si>
+  <si>
+    <t>Program70</t>
+  </si>
+  <si>
+    <t>Program71</t>
+  </si>
+  <si>
+    <t>Program72</t>
+  </si>
+  <si>
+    <t>Program73</t>
+  </si>
+  <si>
+    <t>Program74</t>
+  </si>
+  <si>
+    <t>Program75</t>
+  </si>
+  <si>
+    <t>Program76</t>
+  </si>
+  <si>
+    <t>Program77</t>
+  </si>
+  <si>
+    <t>Program78</t>
+  </si>
+  <si>
+    <t>Program79</t>
+  </si>
+  <si>
+    <t>Program80</t>
+  </si>
+  <si>
+    <t>Program81</t>
+  </si>
+  <si>
+    <t>Program82</t>
+  </si>
+  <si>
+    <t>Program83</t>
+  </si>
+  <si>
+    <t>Program84</t>
+  </si>
+  <si>
+    <t>Program85</t>
+  </si>
+  <si>
+    <t>Program86</t>
+  </si>
+  <si>
+    <t>Program87</t>
+  </si>
+  <si>
+    <t>Program88</t>
+  </si>
+  <si>
+    <t>Program89</t>
+  </si>
+  <si>
+    <t>Program90</t>
+  </si>
+  <si>
+    <t>Program91</t>
+  </si>
+  <si>
+    <t>Program92</t>
+  </si>
+  <si>
+    <t>Program93</t>
+  </si>
+  <si>
+    <t>Program94</t>
+  </si>
+  <si>
+    <t>Program95</t>
+  </si>
+  <si>
+    <t>Program96</t>
+  </si>
+  <si>
+    <t>Program97</t>
+  </si>
+  <si>
+    <t>Program98</t>
+  </si>
+  <si>
+    <t>Program99</t>
+  </si>
+  <si>
+    <t>Program100</t>
+  </si>
+  <si>
+    <t>Program101</t>
+  </si>
+  <si>
+    <t>Program102</t>
+  </si>
+  <si>
+    <t>Program103</t>
+  </si>
+  <si>
+    <t>Program104</t>
+  </si>
+  <si>
+    <t>Program105</t>
+  </si>
+  <si>
+    <t>Program106</t>
+  </si>
+  <si>
+    <t>Program107</t>
+  </si>
+  <si>
+    <t>Program108</t>
+  </si>
+  <si>
+    <t>Program109</t>
+  </si>
+  <si>
+    <t>Program110</t>
+  </si>
+  <si>
+    <t>Program111</t>
+  </si>
+  <si>
+    <t>Program112</t>
+  </si>
+  <si>
+    <t>Program113</t>
+  </si>
+  <si>
+    <t>Program114</t>
+  </si>
+  <si>
+    <t>Program115</t>
+  </si>
+  <si>
+    <t>Program116</t>
+  </si>
+  <si>
+    <t>Program117</t>
+  </si>
+  <si>
+    <t>Program118</t>
+  </si>
+  <si>
+    <t>Program119</t>
+  </si>
+  <si>
+    <t>Program120</t>
+  </si>
+  <si>
+    <t>Program121</t>
+  </si>
+  <si>
+    <t>Program122</t>
+  </si>
+  <si>
+    <t>Program123</t>
+  </si>
+  <si>
+    <t>Program124</t>
+  </si>
+  <si>
+    <t>Program125</t>
+  </si>
+  <si>
+    <t>Program126</t>
+  </si>
+  <si>
+    <t>Program127</t>
+  </si>
+  <si>
+    <t>Program128</t>
+  </si>
+  <si>
+    <t>Program129</t>
+  </si>
+  <si>
+    <t>Program130</t>
+  </si>
+  <si>
+    <t>Program131</t>
+  </si>
+  <si>
+    <t>Program132</t>
+  </si>
+  <si>
+    <t>Program133</t>
+  </si>
+  <si>
+    <t>Program134</t>
+  </si>
+  <si>
+    <t>Program135</t>
+  </si>
+  <si>
+    <t>Program136</t>
+  </si>
+  <si>
+    <t>Program137</t>
+  </si>
+  <si>
+    <t>Program138</t>
+  </si>
+  <si>
+    <t>Program139</t>
+  </si>
+  <si>
+    <t>Program140</t>
+  </si>
+  <si>
+    <t>Program141</t>
+  </si>
+  <si>
+    <t>Program142</t>
+  </si>
+  <si>
+    <t>Program143</t>
+  </si>
+  <si>
+    <t>Program144</t>
+  </si>
+  <si>
+    <t>Program145</t>
+  </si>
+  <si>
+    <t>Program146</t>
+  </si>
+  <si>
+    <t>Program147</t>
+  </si>
+  <si>
+    <t>Program148</t>
+  </si>
+  <si>
+    <t>Program149</t>
+  </si>
+  <si>
+    <t>Program150</t>
+  </si>
+  <si>
+    <t>Program151</t>
+  </si>
+  <si>
+    <t>Program152</t>
+  </si>
+  <si>
+    <t>Program153</t>
+  </si>
+  <si>
+    <t>Program154</t>
+  </si>
+  <si>
+    <t>Program155</t>
+  </si>
+  <si>
+    <t>Program156</t>
+  </si>
+  <si>
+    <t>Program157</t>
+  </si>
+  <si>
+    <t>Program158</t>
+  </si>
+  <si>
+    <t>Program159</t>
+  </si>
+  <si>
+    <t>Program160</t>
+  </si>
+  <si>
+    <t>Program161</t>
+  </si>
+  <si>
+    <t>Program162</t>
+  </si>
+  <si>
+    <t>Program163</t>
+  </si>
+  <si>
+    <t>Program164</t>
+  </si>
+  <si>
+    <t>Program165</t>
+  </si>
+  <si>
+    <t>Program166</t>
+  </si>
+  <si>
+    <t>Program167</t>
+  </si>
+  <si>
+    <t>Program168</t>
+  </si>
+  <si>
+    <t>Program169</t>
+  </si>
+  <si>
+    <t>Program170</t>
+  </si>
+  <si>
+    <t>Program171</t>
+  </si>
+  <si>
+    <t>Program172</t>
+  </si>
+  <si>
+    <t>Program173</t>
+  </si>
+  <si>
+    <t>Program174</t>
+  </si>
+  <si>
+    <t>Program175</t>
+  </si>
+  <si>
+    <t>Program176</t>
+  </si>
+  <si>
+    <t>Program177</t>
+  </si>
+  <si>
+    <t>Program178</t>
+  </si>
+  <si>
+    <t>Program179</t>
+  </si>
+  <si>
+    <t>Program180</t>
+  </si>
+  <si>
+    <t>Program181</t>
+  </si>
+  <si>
+    <t>Program182</t>
+  </si>
+  <si>
+    <t>Program183</t>
+  </si>
+  <si>
+    <t>Program184</t>
+  </si>
+  <si>
+    <t>Program185</t>
+  </si>
+  <si>
+    <t>Program186</t>
+  </si>
+  <si>
+    <t>Program187</t>
+  </si>
+  <si>
+    <t>Program188</t>
+  </si>
+  <si>
+    <t>Program189</t>
+  </si>
+  <si>
+    <t>Program190</t>
+  </si>
+  <si>
+    <t>Program191</t>
+  </si>
+  <si>
+    <t>Program192</t>
+  </si>
+  <si>
+    <t>Program193</t>
+  </si>
+  <si>
+    <t>Program194</t>
+  </si>
+  <si>
+    <t>Program195</t>
+  </si>
+  <si>
+    <t>Program196</t>
+  </si>
+  <si>
+    <t>Program197</t>
+  </si>
+  <si>
+    <t>Program198</t>
+  </si>
+  <si>
+    <t>Program199</t>
+  </si>
+  <si>
+    <t>JavaScript</t>
+  </si>
+  <si>
+    <t>Jay Ganesh Using Console.log("Jay Ganesh")</t>
+  </si>
+  <si>
+    <t>Variable in JavaScript var,let(redeclaration not allowed),Const (Value can changed)</t>
+  </si>
+  <si>
+    <t>Set  In Python Empty set can be created by set({})</t>
+  </si>
+  <si>
+    <t>Dictionary in Python and understanding difference between dic.get("key") and dic.["key"]</t>
+  </si>
+  <si>
+    <t>Function(def) Default Argument Function</t>
+  </si>
+  <si>
+    <t>KeyWord Argument Funcition</t>
+  </si>
+  <si>
+    <t>Program 21</t>
+  </si>
+  <si>
+    <t>Program 22</t>
+  </si>
+  <si>
+    <t>Program 23</t>
+  </si>
+  <si>
+    <t>Program 24</t>
+  </si>
+  <si>
+    <t>Program 25</t>
+  </si>
+  <si>
+    <t>Program 26</t>
+  </si>
+  <si>
+    <t>Program 27</t>
+  </si>
+  <si>
+    <t>Program 28</t>
+  </si>
+  <si>
+    <t>Program 29</t>
+  </si>
+  <si>
+    <t>Program 30</t>
+  </si>
+  <si>
+    <t>Program 31</t>
+  </si>
+  <si>
+    <t>Program 32</t>
+  </si>
+  <si>
+    <t>Program 33</t>
+  </si>
+  <si>
+    <t>Program 34</t>
+  </si>
+  <si>
+    <t>Program 35</t>
+  </si>
+  <si>
+    <t>Program 36</t>
+  </si>
+  <si>
+    <t>Program 37</t>
+  </si>
+  <si>
+    <t>Program 38</t>
+  </si>
+  <si>
+    <t>Program 39</t>
+  </si>
+  <si>
+    <t>Program 40</t>
+  </si>
+  <si>
+    <t>Program 41</t>
+  </si>
+  <si>
+    <t>Program 42</t>
+  </si>
+  <si>
+    <t>Program 43</t>
+  </si>
+  <si>
+    <t>Program 44</t>
+  </si>
+  <si>
+    <t>Program 45</t>
+  </si>
+  <si>
+    <t>Program 46</t>
+  </si>
+  <si>
+    <t>Program 47</t>
+  </si>
+  <si>
+    <t>Program 48</t>
+  </si>
+  <si>
+    <t>Program 49</t>
+  </si>
+  <si>
+    <t>Program 50</t>
+  </si>
+  <si>
+    <t>Program 51</t>
+  </si>
+  <si>
+    <t>Program 52</t>
+  </si>
+  <si>
+    <t>Program 53</t>
+  </si>
+  <si>
+    <t>Program 54</t>
+  </si>
+  <si>
+    <t>Program 55</t>
+  </si>
+  <si>
+    <t>Program 56</t>
+  </si>
+  <si>
+    <t>Program 57</t>
+  </si>
+  <si>
+    <t>Program 58</t>
+  </si>
+  <si>
+    <t>Program 59</t>
+  </si>
+  <si>
+    <t>Program 60</t>
+  </si>
+  <si>
+    <t>Program 61</t>
+  </si>
+  <si>
+    <t>Program 62</t>
+  </si>
+  <si>
+    <t>Program 63</t>
+  </si>
+  <si>
+    <t>Program 64</t>
+  </si>
+  <si>
+    <t>Program 65</t>
+  </si>
+  <si>
+    <t>Program 66</t>
+  </si>
+  <si>
+    <t>Program 67</t>
+  </si>
+  <si>
+    <t>Program 68</t>
+  </si>
+  <si>
+    <t>Program 69</t>
+  </si>
+  <si>
+    <t>Program 70</t>
+  </si>
+  <si>
+    <t>Program 71</t>
+  </si>
+  <si>
+    <t>Program 72</t>
+  </si>
+  <si>
+    <t>Program 73</t>
+  </si>
+  <si>
+    <t>Program 74</t>
+  </si>
+  <si>
+    <t>Program 75</t>
+  </si>
+  <si>
+    <t>Program 76</t>
+  </si>
+  <si>
+    <t>Program 77</t>
+  </si>
+  <si>
+    <t>Program 78</t>
+  </si>
+  <si>
+    <t>Program 79</t>
+  </si>
+  <si>
+    <t>Program 80</t>
+  </si>
+  <si>
+    <t>Program 81</t>
+  </si>
+  <si>
+    <t>Program 82</t>
+  </si>
+  <si>
+    <t>Program 83</t>
+  </si>
+  <si>
+    <t>Program 84</t>
+  </si>
+  <si>
+    <t>Program 85</t>
+  </si>
+  <si>
+    <t>Program 86</t>
+  </si>
+  <si>
+    <t>Program 87</t>
+  </si>
+  <si>
+    <t>Program 88</t>
+  </si>
+  <si>
+    <t>Program 89</t>
+  </si>
+  <si>
+    <t>Program 90</t>
+  </si>
+  <si>
+    <t>Program 91</t>
+  </si>
+  <si>
+    <t>Program 92</t>
+  </si>
+  <si>
+    <t>Program 93</t>
+  </si>
+  <si>
+    <t>Program 94</t>
+  </si>
+  <si>
+    <t>Program 95</t>
+  </si>
+  <si>
+    <t>Program 96</t>
+  </si>
+  <si>
+    <t>Program 97</t>
+  </si>
+  <si>
+    <t>Program 98</t>
+  </si>
+  <si>
+    <t>Program 99</t>
+  </si>
+  <si>
+    <t>Program 100</t>
+  </si>
+  <si>
+    <t>Program 101</t>
+  </si>
+  <si>
+    <t>Program 102</t>
+  </si>
+  <si>
+    <t>Program 103</t>
+  </si>
+  <si>
+    <t>Program 104</t>
+  </si>
+  <si>
+    <t>Program 105</t>
+  </si>
+  <si>
+    <t>Program 106</t>
+  </si>
+  <si>
+    <t>Program 107</t>
+  </si>
+  <si>
+    <t>Program 108</t>
+  </si>
+  <si>
+    <t>Program 109</t>
+  </si>
+  <si>
+    <t>Program 110</t>
+  </si>
+  <si>
+    <t>Program 111</t>
+  </si>
+  <si>
+    <t>Program 112</t>
+  </si>
+  <si>
+    <t>Program 113</t>
+  </si>
+  <si>
+    <t>Program 114</t>
+  </si>
+  <si>
+    <t>Program 115</t>
+  </si>
+  <si>
+    <t>Program 116</t>
+  </si>
+  <si>
+    <t>Program 117</t>
+  </si>
+  <si>
+    <t>Program 118</t>
+  </si>
+  <si>
+    <t>Program 119</t>
+  </si>
+  <si>
+    <t>Program 120</t>
+  </si>
+  <si>
+    <t>Program 121</t>
+  </si>
+  <si>
+    <t>Program 122</t>
+  </si>
+  <si>
+    <t>Program 123</t>
+  </si>
+  <si>
+    <t>Program 124</t>
+  </si>
+  <si>
+    <t>Program 125</t>
+  </si>
+  <si>
+    <t>Program 126</t>
+  </si>
+  <si>
+    <t>Program 127</t>
+  </si>
+  <si>
+    <t>Program 128</t>
+  </si>
+  <si>
+    <t>Program 129</t>
+  </si>
+  <si>
+    <t>Program 130</t>
+  </si>
+  <si>
+    <t>Program 131</t>
+  </si>
+  <si>
+    <t>Program 132</t>
+  </si>
+  <si>
+    <t>Program 133</t>
+  </si>
+  <si>
+    <t>Program 134</t>
+  </si>
+  <si>
+    <t>Program 135</t>
+  </si>
+  <si>
+    <t>Program 136</t>
+  </si>
+  <si>
+    <t>Program 137</t>
+  </si>
+  <si>
+    <t>Program 138</t>
+  </si>
+  <si>
+    <t>Program 139</t>
+  </si>
+  <si>
+    <t>Program 140</t>
+  </si>
+  <si>
+    <t>Program 141</t>
+  </si>
+  <si>
+    <t>Program 142</t>
+  </si>
+  <si>
+    <t>Program 143</t>
+  </si>
+  <si>
+    <t>Positional Arguments in Python</t>
+  </si>
+  <si>
+    <t>Arbitrary function *args and **kargs</t>
+  </si>
+  <si>
+    <t>Funciton with multiple return values</t>
+  </si>
+  <si>
+    <t>Anonymos Funciton in python (Lambda Function)</t>
+  </si>
+  <si>
+    <t>Filter + Function(LLambda) And map + Function(lambda)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pass By Value </t>
+  </si>
+  <si>
+    <t>Pass By refrence By List and or dictionary</t>
+  </si>
+  <si>
+    <t>File Handling (File Proporties)</t>
+  </si>
+  <si>
+    <t>Reading the content from file</t>
+  </si>
+  <si>
+    <t>Writing the content in file</t>
+  </si>
+  <si>
+    <t>Reading the content from file read(byte),readline(),readlines()</t>
+  </si>
+  <si>
+    <t>Writing the content in file write(),writelines()</t>
+  </si>
+  <si>
+    <t>seek() Manipulating file pointer and tell() File pointer position</t>
+  </si>
+  <si>
+    <t>Delete Operation imposrt os module</t>
+  </si>
+  <si>
+    <t>Exception handling try,exceptio,finally</t>
+  </si>
+  <si>
+    <t>Handling a Exception</t>
+  </si>
+  <si>
+    <t>Accepting a multiple input</t>
+  </si>
+  <si>
+    <t>OOP creating class and calling constructur</t>
+  </si>
+  <si>
+    <t>OOP understanding class(static) and Instance method(non-static method) And all function required self as a first parameter</t>
+  </si>
+  <si>
+    <t>OOP understanding constructor and destructor</t>
   </si>
 </sst>
 </file>
@@ -205,14 +1259,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -547,12 +1606,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19D1B62-8AB4-4DE6-A4B9-DCFE9C1F8102}">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C145"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="92.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="102" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -731,52 +1790,2742 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>17</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
       <c r="B19" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
       <c r="B21" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C21" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>21</v>
       </c>
       <c r="B22" t="s">
         <v>23</v>
+      </c>
+      <c r="C22" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A125" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A126" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A127" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A128" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A129" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A130" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A131" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A132" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A133" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A134" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A135" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A136" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A137" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A138" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A139" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A140" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A141" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A142" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A143" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A144" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A145" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43850411-BEF7-434C-A82A-CCD83C8B451E}">
+  <dimension ref="A1:C201"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="73.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A125" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A126" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A127" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A128" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A129" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A130" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A131" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A132" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A133" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A134" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A135" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A136" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A137" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A138" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A139" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A140" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A141" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A142" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A143" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A144" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A145" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A146" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A147" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A148" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A149" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A150" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A151" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A152" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A153" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A154" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A155" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A156" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A157" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A158" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A159" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A160" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A161" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A163" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A165" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A167" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A169" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A170" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A171" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A172" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A173" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A174" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A175" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A176" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A177" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A178" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A179" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A180" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A181" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A182" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A183" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A184" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A185" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A186" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A187" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A188" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A189" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A190" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A191" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A192" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A193" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A194" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A195" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A196" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A197" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A198" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A199" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A200" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A201" s="3" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/Pyhton Programs.xlsx
+++ b/Pyhton Programs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workplace\Python-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8567D43E-B80F-4632-97DD-31C956B9E70F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1666E250-68A5-4303-A516-7A43213AB3AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
   </bookViews>
   <sheets>
     <sheet name="Python" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="406">
   <si>
     <t>Program NO</t>
   </si>
@@ -114,9 +114,6 @@
     <t>Print Inbuilt method</t>
   </si>
   <si>
-    <t>Address And Refrence comprsion</t>
-  </si>
-  <si>
     <t>program</t>
   </si>
   <si>
@@ -1210,6 +1207,54 @@
   </si>
   <si>
     <t>OOP understanding constructor and destructor</t>
+  </si>
+  <si>
+    <t>OOP Method redefination(Method Overiding)</t>
+  </si>
+  <si>
+    <t>Static Charactersrics (Class Variable) and Non-Static Characterstics(Instance Variable)</t>
+  </si>
+  <si>
+    <t>Static Method @staticMethod (Behaviour) and Non-Static Method(Function)</t>
+  </si>
+  <si>
+    <t>OOP Single Level Inheritance and calling explicitly to Base class Constructor from Derived Class Constructor Super().__init()__</t>
+  </si>
+  <si>
+    <t>OOP Constructor Calling Sequence and Destructor Callling Sequence</t>
+  </si>
+  <si>
+    <t>OOP Multiple Level Inheritance and Calling Sequence Of Constructor And Destructor</t>
+  </si>
+  <si>
+    <t>OOP MultiLevel Inheritance Constructor Calling Sequence And Destructor Callifn Sequence</t>
+  </si>
+  <si>
+    <t>OOP MultiLevel Inheritance Constructor Calling Sequence And Destructor Callifn Sequence Adding Super</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOP hierarchical inheritance </t>
+  </si>
+  <si>
+    <t>Packages in Python</t>
+  </si>
+  <si>
+    <t>Address And Refrence comparsion</t>
+  </si>
+  <si>
+    <t>Difference Between == and === operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input and output using </t>
+  </si>
+  <si>
+    <t>in operator in javascript</t>
+  </si>
+  <si>
+    <t>Control Statement</t>
+  </si>
+  <si>
+    <t>For , While,do_while loop</t>
   </si>
 </sst>
 </file>
@@ -1259,7 +1304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1267,11 +1312,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1627,7 +1667,7 @@
     </row>
     <row r="2" spans="1:3" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>23</v>
@@ -1644,7 +1684,7 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1655,7 +1695,7 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1666,7 +1706,7 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1677,7 +1717,7 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1688,7 +1728,7 @@
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1699,7 +1739,7 @@
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -1710,7 +1750,7 @@
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -1721,7 +1761,7 @@
         <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -1732,7 +1772,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -1743,7 +1783,7 @@
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -1754,7 +1794,7 @@
         <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -1765,7 +1805,7 @@
         <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -1776,7 +1816,7 @@
         <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -1787,7 +1827,7 @@
         <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -1798,7 +1838,7 @@
         <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -1809,7 +1849,7 @@
         <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -1820,7 +1860,7 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -1831,7 +1871,7 @@
         <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -1842,7 +1882,7 @@
         <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -1853,1050 +1893,1080 @@
         <v>23</v>
       </c>
       <c r="C22" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>248</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="B24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>249</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>250</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="B26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>251</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>252</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="B28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>253</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="B29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>254</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="B30" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>255</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="B31" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>256</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="B32" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>257</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="B33" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>258</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="B34" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>259</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="B35" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>260</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="B36" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>261</v>
+      </c>
+      <c r="B37" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>262</v>
+      </c>
+      <c r="B38" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C36" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C37" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>263</v>
+      </c>
+      <c r="B39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C38" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>264</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="B40" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>265</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="B41" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>266</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C41" s="5" t="s">
+      <c r="B42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>267</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C42" s="5" t="s">
+      <c r="B43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>268</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
+      <c r="B44" t="s">
+        <v>23</v>
+      </c>
+      <c r="C44" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>269</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
+      <c r="B45" t="s">
+        <v>23</v>
+      </c>
+      <c r="C45" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>270</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="3" t="s">
+      <c r="B46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C46" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>271</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="3" t="s">
+      <c r="B47" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>272</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="3" t="s">
+      <c r="B48" t="s">
+        <v>23</v>
+      </c>
+      <c r="C48" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>273</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="3" t="s">
+      <c r="B49" t="s">
+        <v>23</v>
+      </c>
+      <c r="C49" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>274</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="3" t="s">
+      <c r="B50" t="s">
+        <v>23</v>
+      </c>
+      <c r="C50" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>275</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="3" t="s">
+      <c r="B51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C51" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>276</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="3" t="s">
+      <c r="B52" t="s">
+        <v>23</v>
+      </c>
+      <c r="C52" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>277</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="3" t="s">
+      <c r="B53" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>278</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="3" t="s">
+      <c r="B54" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>279</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="3" t="s">
+      <c r="B55" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>280</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="3" t="s">
+      <c r="B56" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>281</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="3" t="s">
+      <c r="B57" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>282</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="3" t="s">
+      <c r="B58" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>283</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="3" t="s">
+      <c r="B59" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>284</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="3" t="s">
+      <c r="B60" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>285</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="3" t="s">
+      <c r="B61" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>286</v>
       </c>
-      <c r="B61" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="3" t="s">
+      <c r="B62" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>287</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="3" t="s">
+      <c r="B63" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>288</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="3" t="s">
+      <c r="B64" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>289</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="3" t="s">
+      <c r="B65" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>290</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="3" t="s">
+      <c r="B66" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>291</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="3" t="s">
+      <c r="B67" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>292</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="3" t="s">
+      <c r="B68" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>293</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="3" t="s">
+      <c r="B69" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>294</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="3" t="s">
+      <c r="B70" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>295</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="3" t="s">
+      <c r="B71" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>296</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="3" t="s">
+      <c r="B72" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>297</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="3" t="s">
+      <c r="B73" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>298</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="3" t="s">
+      <c r="B74" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>299</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="3" t="s">
+      <c r="B75" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>300</v>
       </c>
-      <c r="B75" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="3" t="s">
+      <c r="B76" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>301</v>
       </c>
-      <c r="B76" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="3" t="s">
+      <c r="B77" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>302</v>
       </c>
-      <c r="B77" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="3" t="s">
+      <c r="B78" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>303</v>
       </c>
-      <c r="B78" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="3" t="s">
+      <c r="B79" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>304</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="3" t="s">
+      <c r="B80" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>305</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" s="3" t="s">
+      <c r="B81" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
         <v>306</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" s="3" t="s">
+      <c r="B82" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
         <v>307</v>
       </c>
-      <c r="B82" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" s="3" t="s">
+      <c r="B83" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>308</v>
       </c>
-      <c r="B83" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A84" s="3" t="s">
+      <c r="B84" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
         <v>309</v>
       </c>
-      <c r="B84" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A85" s="3" t="s">
+      <c r="B85" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
         <v>310</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86" s="3" t="s">
+      <c r="B86" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
         <v>311</v>
       </c>
-      <c r="B86" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A87" s="3" t="s">
+      <c r="B87" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
         <v>312</v>
       </c>
-      <c r="B87" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A88" s="3" t="s">
+      <c r="B88" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
         <v>313</v>
       </c>
-      <c r="B88" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A89" s="3" t="s">
+      <c r="B89" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
         <v>314</v>
       </c>
-      <c r="B89" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A90" s="3" t="s">
+      <c r="B90" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
         <v>315</v>
       </c>
-      <c r="B90" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A91" s="3" t="s">
+      <c r="B91" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
         <v>316</v>
       </c>
-      <c r="B91" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A92" s="3" t="s">
+      <c r="B92" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
         <v>317</v>
       </c>
-      <c r="B92" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A93" s="3" t="s">
+      <c r="B93" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
         <v>318</v>
       </c>
-      <c r="B93" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A94" s="3" t="s">
+      <c r="B94" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
         <v>319</v>
       </c>
-      <c r="B94" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A95" s="3" t="s">
+      <c r="B95" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
         <v>320</v>
       </c>
-      <c r="B95" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A96" s="3" t="s">
+      <c r="B96" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
         <v>321</v>
       </c>
-      <c r="B96" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A97" s="3" t="s">
+      <c r="B97" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
         <v>322</v>
       </c>
-      <c r="B97" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A98" s="3" t="s">
+      <c r="B98" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
         <v>323</v>
       </c>
-      <c r="B98" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A99" s="3" t="s">
+      <c r="B99" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
         <v>324</v>
       </c>
-      <c r="B99" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A100" s="3" t="s">
+      <c r="B100" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
         <v>325</v>
       </c>
-      <c r="B100" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A101" s="3" t="s">
+      <c r="B101" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
         <v>326</v>
       </c>
-      <c r="B101" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A102" s="3" t="s">
+      <c r="B102" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
         <v>327</v>
       </c>
-      <c r="B102" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A103" s="3" t="s">
+      <c r="B103" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
         <v>328</v>
       </c>
-      <c r="B103" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A104" s="3" t="s">
+      <c r="B104" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
         <v>329</v>
       </c>
-      <c r="B104" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A105" s="3" t="s">
+      <c r="B105" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
         <v>330</v>
       </c>
-      <c r="B105" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A106" s="3" t="s">
+      <c r="B106" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
         <v>331</v>
       </c>
-      <c r="B106" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A107" s="3" t="s">
+      <c r="B107" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
         <v>332</v>
       </c>
-      <c r="B107" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A108" s="3" t="s">
+      <c r="B108" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
         <v>333</v>
       </c>
-      <c r="B108" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A109" s="3" t="s">
+      <c r="B109" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
         <v>334</v>
       </c>
-      <c r="B109" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A110" s="3" t="s">
+      <c r="B110" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
         <v>335</v>
       </c>
-      <c r="B110" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A111" s="3" t="s">
+      <c r="B111" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
         <v>336</v>
       </c>
-      <c r="B111" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A112" s="3" t="s">
+      <c r="B112" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
         <v>337</v>
       </c>
-      <c r="B112" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A113" s="3" t="s">
+      <c r="B113" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
         <v>338</v>
       </c>
-      <c r="B113" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A114" s="3" t="s">
+      <c r="B114" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
         <v>339</v>
       </c>
-      <c r="B114" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A115" s="3" t="s">
+      <c r="B115" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
         <v>340</v>
       </c>
-      <c r="B115" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A116" s="3" t="s">
+      <c r="B116" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
         <v>341</v>
       </c>
-      <c r="B116" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A117" s="3" t="s">
+      <c r="B117" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
         <v>342</v>
       </c>
-      <c r="B117" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A118" s="3" t="s">
+      <c r="B118" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
         <v>343</v>
       </c>
-      <c r="B118" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A119" s="3" t="s">
+      <c r="B119" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
         <v>344</v>
       </c>
-      <c r="B119" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A120" s="3" t="s">
+      <c r="B120" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
         <v>345</v>
       </c>
-      <c r="B120" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A121" s="3" t="s">
+      <c r="B121" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
         <v>346</v>
       </c>
-      <c r="B121" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A122" s="3" t="s">
+      <c r="B122" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
         <v>347</v>
       </c>
-      <c r="B122" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A123" s="3" t="s">
+      <c r="B123" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
         <v>348</v>
       </c>
-      <c r="B123" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A124" s="3" t="s">
+      <c r="B124" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
         <v>349</v>
       </c>
-      <c r="B124" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A125" s="3" t="s">
+      <c r="B125" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
         <v>350</v>
       </c>
-      <c r="B125" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A126" s="3" t="s">
+      <c r="B126" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
         <v>351</v>
       </c>
-      <c r="B126" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A127" s="3" t="s">
+      <c r="B127" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
         <v>352</v>
       </c>
-      <c r="B127" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A128" s="3" t="s">
+      <c r="B128" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
         <v>353</v>
       </c>
-      <c r="B128" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A129" s="3" t="s">
+      <c r="B129" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
         <v>354</v>
       </c>
-      <c r="B129" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A130" s="3" t="s">
+      <c r="B130" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
         <v>355</v>
       </c>
-      <c r="B130" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A131" s="3" t="s">
+      <c r="B131" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
         <v>356</v>
       </c>
-      <c r="B131" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A132" s="3" t="s">
+      <c r="B132" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
         <v>357</v>
       </c>
-      <c r="B132" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A133" s="3" t="s">
+      <c r="B133" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
         <v>358</v>
       </c>
-      <c r="B133" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A134" s="3" t="s">
+      <c r="B134" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
         <v>359</v>
       </c>
-      <c r="B134" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A135" s="3" t="s">
+      <c r="B135" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
         <v>360</v>
       </c>
-      <c r="B135" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A136" s="3" t="s">
+      <c r="B136" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
         <v>361</v>
       </c>
-      <c r="B136" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A137" s="3" t="s">
+      <c r="B137" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
         <v>362</v>
       </c>
-      <c r="B137" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A138" s="3" t="s">
+      <c r="B138" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
         <v>363</v>
       </c>
-      <c r="B138" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A139" s="3" t="s">
+      <c r="B139" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
         <v>364</v>
       </c>
-      <c r="B139" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A140" s="3" t="s">
+      <c r="B140" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
         <v>365</v>
       </c>
-      <c r="B140" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A141" s="3" t="s">
+      <c r="B141" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
         <v>366</v>
       </c>
-      <c r="B141" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A142" s="3" t="s">
+      <c r="B142" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
         <v>367</v>
       </c>
-      <c r="B142" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A143" s="3" t="s">
+      <c r="B143" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
         <v>368</v>
       </c>
-      <c r="B143" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A144" s="3" t="s">
+      <c r="B144" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
         <v>369</v>
       </c>
-      <c r="B144" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A145" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="B145" s="3" t="s">
+      <c r="B145" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2918,1614 +2988,1629 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C2" t="s">
         <v>241</v>
-      </c>
-      <c r="C2" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>241</v>
+        <v>41</v>
+      </c>
+      <c r="B3" t="s">
+        <v>240</v>
       </c>
       <c r="C3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>241</v>
+        <v>42</v>
+      </c>
+      <c r="B4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C4" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C5" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="B6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C6" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="B7" t="s">
+        <v>240</v>
+      </c>
+      <c r="C7" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="B8" t="s">
+        <v>240</v>
+      </c>
+      <c r="C8" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+      <c r="B9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="B10" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="B11" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="B12" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="B13" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="B14" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="B15" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="B16" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="B17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+      <c r="B18" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+      <c r="B19" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+      <c r="B20" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+      <c r="B21" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>60</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
+      <c r="B22" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+      <c r="B23" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>62</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
+      <c r="B24" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>63</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
+      <c r="B25" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>64</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
+      <c r="B26" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>65</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
+      <c r="B27" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>66</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+      <c r="B28" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>67</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
+      <c r="B29" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>68</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
+      <c r="B30" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
+      <c r="B31" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
+      <c r="B32" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
+      <c r="B33" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
+      <c r="B34" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>73</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
+      <c r="B35" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>74</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="3" t="s">
+      <c r="B36" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>75</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="3" t="s">
+      <c r="B37" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>76</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
+      <c r="B38" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
+      <c r="B39" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>78</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
+      <c r="B40" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>79</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
+      <c r="B41" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>80</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
+      <c r="B42" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>81</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
+      <c r="B43" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>82</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
+      <c r="B44" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>83</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
+      <c r="B45" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>84</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="3" t="s">
+      <c r="B46" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>85</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="3" t="s">
+      <c r="B47" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>86</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="3" t="s">
+      <c r="B48" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>87</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="3" t="s">
+      <c r="B49" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>88</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="3" t="s">
+      <c r="B50" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>89</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="3" t="s">
+      <c r="B51" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>90</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="3" t="s">
+      <c r="B52" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>91</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="3" t="s">
+      <c r="B53" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>92</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="3" t="s">
+      <c r="B54" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>93</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="3" t="s">
+      <c r="B55" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>94</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="3" t="s">
+      <c r="B56" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>95</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="3" t="s">
+      <c r="B57" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>96</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="3" t="s">
+      <c r="B58" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>97</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="3" t="s">
+      <c r="B59" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>98</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="3" t="s">
+      <c r="B60" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>99</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="3" t="s">
+      <c r="B61" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>100</v>
       </c>
-      <c r="B61" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="3" t="s">
+      <c r="B62" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>101</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="3" t="s">
+      <c r="B63" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>102</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="3" t="s">
+      <c r="B64" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>103</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="3" t="s">
+      <c r="B65" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>104</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="3" t="s">
+      <c r="B66" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>105</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="3" t="s">
+      <c r="B67" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>106</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="3" t="s">
+      <c r="B68" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>107</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="3" t="s">
+      <c r="B69" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>108</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="3" t="s">
+      <c r="B70" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>109</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="3" t="s">
+      <c r="B71" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>110</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="3" t="s">
+      <c r="B72" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>111</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="3" t="s">
+      <c r="B73" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>112</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="3" t="s">
+      <c r="B74" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>113</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="3" t="s">
+      <c r="B75" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>114</v>
       </c>
-      <c r="B75" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="3" t="s">
+      <c r="B76" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>115</v>
       </c>
-      <c r="B76" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="3" t="s">
+      <c r="B77" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>116</v>
       </c>
-      <c r="B77" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="3" t="s">
+      <c r="B78" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>117</v>
       </c>
-      <c r="B78" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="3" t="s">
+      <c r="B79" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>118</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="3" t="s">
+      <c r="B80" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>119</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" s="3" t="s">
+      <c r="B81" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
         <v>120</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" s="3" t="s">
+      <c r="B82" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
         <v>121</v>
       </c>
-      <c r="B82" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" s="3" t="s">
+      <c r="B83" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>122</v>
       </c>
-      <c r="B83" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A84" s="3" t="s">
+      <c r="B84" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
         <v>123</v>
       </c>
-      <c r="B84" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A85" s="3" t="s">
+      <c r="B85" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
         <v>124</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86" s="3" t="s">
+      <c r="B86" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
         <v>125</v>
       </c>
-      <c r="B86" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A87" s="3" t="s">
+      <c r="B87" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
         <v>126</v>
       </c>
-      <c r="B87" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A88" s="3" t="s">
+      <c r="B88" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
         <v>127</v>
       </c>
-      <c r="B88" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A89" s="3" t="s">
+      <c r="B89" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
         <v>128</v>
       </c>
-      <c r="B89" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A90" s="3" t="s">
+      <c r="B90" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
         <v>129</v>
       </c>
-      <c r="B90" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A91" s="3" t="s">
+      <c r="B91" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
         <v>130</v>
       </c>
-      <c r="B91" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A92" s="3" t="s">
+      <c r="B92" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
         <v>131</v>
       </c>
-      <c r="B92" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A93" s="3" t="s">
+      <c r="B93" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
         <v>132</v>
       </c>
-      <c r="B93" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A94" s="3" t="s">
+      <c r="B94" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
         <v>133</v>
       </c>
-      <c r="B94" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A95" s="3" t="s">
+      <c r="B95" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
         <v>134</v>
       </c>
-      <c r="B95" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A96" s="3" t="s">
+      <c r="B96" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
         <v>135</v>
       </c>
-      <c r="B96" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A97" s="3" t="s">
+      <c r="B97" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
         <v>136</v>
       </c>
-      <c r="B97" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A98" s="3" t="s">
+      <c r="B98" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
         <v>137</v>
       </c>
-      <c r="B98" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A99" s="3" t="s">
+      <c r="B99" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
         <v>138</v>
       </c>
-      <c r="B99" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A100" s="3" t="s">
+      <c r="B100" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
         <v>139</v>
       </c>
-      <c r="B100" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A101" s="3" t="s">
+      <c r="B101" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
         <v>140</v>
       </c>
-      <c r="B101" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A102" s="3" t="s">
+      <c r="B102" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
         <v>141</v>
       </c>
-      <c r="B102" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A103" s="3" t="s">
+      <c r="B103" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
         <v>142</v>
       </c>
-      <c r="B103" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A104" s="3" t="s">
+      <c r="B104" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
         <v>143</v>
       </c>
-      <c r="B104" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A105" s="3" t="s">
+      <c r="B105" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
         <v>144</v>
       </c>
-      <c r="B105" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A106" s="3" t="s">
+      <c r="B106" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
         <v>145</v>
       </c>
-      <c r="B106" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A107" s="3" t="s">
+      <c r="B107" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
         <v>146</v>
       </c>
-      <c r="B107" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A108" s="3" t="s">
+      <c r="B108" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
         <v>147</v>
       </c>
-      <c r="B108" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A109" s="3" t="s">
+      <c r="B109" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
         <v>148</v>
       </c>
-      <c r="B109" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A110" s="3" t="s">
+      <c r="B110" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
         <v>149</v>
       </c>
-      <c r="B110" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A111" s="3" t="s">
+      <c r="B111" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
         <v>150</v>
       </c>
-      <c r="B111" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A112" s="3" t="s">
+      <c r="B112" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
         <v>151</v>
       </c>
-      <c r="B112" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A113" s="3" t="s">
+      <c r="B113" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
         <v>152</v>
       </c>
-      <c r="B113" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A114" s="3" t="s">
+      <c r="B114" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
         <v>153</v>
       </c>
-      <c r="B114" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A115" s="3" t="s">
+      <c r="B115" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
         <v>154</v>
       </c>
-      <c r="B115" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A116" s="3" t="s">
+      <c r="B116" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
         <v>155</v>
       </c>
-      <c r="B116" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A117" s="3" t="s">
+      <c r="B117" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
         <v>156</v>
       </c>
-      <c r="B117" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A118" s="3" t="s">
+      <c r="B118" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
         <v>157</v>
       </c>
-      <c r="B118" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A119" s="3" t="s">
+      <c r="B119" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
         <v>158</v>
       </c>
-      <c r="B119" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A120" s="3" t="s">
+      <c r="B120" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
         <v>159</v>
       </c>
-      <c r="B120" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A121" s="3" t="s">
+      <c r="B121" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
         <v>160</v>
       </c>
-      <c r="B121" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A122" s="3" t="s">
+      <c r="B122" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
         <v>161</v>
       </c>
-      <c r="B122" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A123" s="3" t="s">
+      <c r="B123" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
         <v>162</v>
       </c>
-      <c r="B123" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A124" s="3" t="s">
+      <c r="B124" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
         <v>163</v>
       </c>
-      <c r="B124" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A125" s="3" t="s">
+      <c r="B125" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
         <v>164</v>
       </c>
-      <c r="B125" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A126" s="3" t="s">
+      <c r="B126" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
         <v>165</v>
       </c>
-      <c r="B126" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A127" s="3" t="s">
+      <c r="B127" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
         <v>166</v>
       </c>
-      <c r="B127" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A128" s="3" t="s">
+      <c r="B128" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
         <v>167</v>
       </c>
-      <c r="B128" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A129" s="3" t="s">
+      <c r="B129" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
         <v>168</v>
       </c>
-      <c r="B129" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A130" s="3" t="s">
+      <c r="B130" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
         <v>169</v>
       </c>
-      <c r="B130" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A131" s="3" t="s">
+      <c r="B131" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
         <v>170</v>
       </c>
-      <c r="B131" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A132" s="3" t="s">
+      <c r="B132" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
         <v>171</v>
       </c>
-      <c r="B132" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A133" s="3" t="s">
+      <c r="B133" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
         <v>172</v>
       </c>
-      <c r="B133" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A134" s="3" t="s">
+      <c r="B134" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
         <v>173</v>
       </c>
-      <c r="B134" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A135" s="3" t="s">
+      <c r="B135" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
         <v>174</v>
       </c>
-      <c r="B135" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A136" s="3" t="s">
+      <c r="B136" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
         <v>175</v>
       </c>
-      <c r="B136" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A137" s="3" t="s">
+      <c r="B137" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
         <v>176</v>
       </c>
-      <c r="B137" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A138" s="3" t="s">
+      <c r="B138" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
         <v>177</v>
       </c>
-      <c r="B138" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A139" s="3" t="s">
+      <c r="B139" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
         <v>178</v>
       </c>
-      <c r="B139" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A140" s="3" t="s">
+      <c r="B140" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
         <v>179</v>
       </c>
-      <c r="B140" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A141" s="3" t="s">
+      <c r="B141" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
         <v>180</v>
       </c>
-      <c r="B141" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A142" s="3" t="s">
+      <c r="B142" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
         <v>181</v>
       </c>
-      <c r="B142" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A143" s="3" t="s">
+      <c r="B143" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
         <v>182</v>
       </c>
-      <c r="B143" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A144" s="3" t="s">
+      <c r="B144" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
         <v>183</v>
       </c>
-      <c r="B144" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A145" s="3" t="s">
+      <c r="B145" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
         <v>184</v>
       </c>
-      <c r="B145" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A146" s="3" t="s">
+      <c r="B146" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
         <v>185</v>
       </c>
-      <c r="B146" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A147" s="3" t="s">
+      <c r="B147" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
         <v>186</v>
       </c>
-      <c r="B147" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A148" s="3" t="s">
+      <c r="B148" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
         <v>187</v>
       </c>
-      <c r="B148" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A149" s="3" t="s">
+      <c r="B149" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
         <v>188</v>
       </c>
-      <c r="B149" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A150" s="3" t="s">
+      <c r="B150" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
         <v>189</v>
       </c>
-      <c r="B150" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A151" s="3" t="s">
+      <c r="B151" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
         <v>190</v>
       </c>
-      <c r="B151" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A152" s="3" t="s">
+      <c r="B152" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
         <v>191</v>
       </c>
-      <c r="B152" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A153" s="3" t="s">
+      <c r="B153" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
         <v>192</v>
       </c>
-      <c r="B153" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A154" s="3" t="s">
+      <c r="B154" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
         <v>193</v>
       </c>
-      <c r="B154" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A155" s="3" t="s">
+      <c r="B155" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
         <v>194</v>
       </c>
-      <c r="B155" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A156" s="3" t="s">
+      <c r="B156" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
         <v>195</v>
       </c>
-      <c r="B156" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A157" s="3" t="s">
+      <c r="B157" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
         <v>196</v>
       </c>
-      <c r="B157" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A158" s="3" t="s">
+      <c r="B158" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
         <v>197</v>
       </c>
-      <c r="B158" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A159" s="3" t="s">
+      <c r="B159" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
         <v>198</v>
       </c>
-      <c r="B159" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A160" s="3" t="s">
+      <c r="B160" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
         <v>199</v>
       </c>
-      <c r="B160" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A161" s="3" t="s">
+      <c r="B161" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
         <v>200</v>
       </c>
-      <c r="B161" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A162" s="3" t="s">
+      <c r="B162" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
         <v>201</v>
       </c>
-      <c r="B162" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A163" s="3" t="s">
+      <c r="B163" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
         <v>202</v>
       </c>
-      <c r="B163" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A164" s="3" t="s">
+      <c r="B164" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
         <v>203</v>
       </c>
-      <c r="B164" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A165" s="3" t="s">
+      <c r="B165" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
         <v>204</v>
       </c>
-      <c r="B165" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A166" s="3" t="s">
+      <c r="B166" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
         <v>205</v>
       </c>
-      <c r="B166" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A167" s="3" t="s">
+      <c r="B167" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
         <v>206</v>
       </c>
-      <c r="B167" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A168" s="3" t="s">
+      <c r="B168" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
         <v>207</v>
       </c>
-      <c r="B168" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A169" s="3" t="s">
+      <c r="B169" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
         <v>208</v>
       </c>
-      <c r="B169" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A170" s="3" t="s">
+      <c r="B170" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
         <v>209</v>
       </c>
-      <c r="B170" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A171" s="3" t="s">
+      <c r="B171" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
         <v>210</v>
       </c>
-      <c r="B171" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A172" s="3" t="s">
+      <c r="B172" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
         <v>211</v>
       </c>
-      <c r="B172" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A173" s="3" t="s">
+      <c r="B173" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
         <v>212</v>
       </c>
-      <c r="B173" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A174" s="3" t="s">
+      <c r="B174" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
         <v>213</v>
       </c>
-      <c r="B174" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A175" s="3" t="s">
+      <c r="B175" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
         <v>214</v>
       </c>
-      <c r="B175" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A176" s="3" t="s">
+      <c r="B176" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
         <v>215</v>
       </c>
-      <c r="B176" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A177" s="3" t="s">
+      <c r="B177" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
         <v>216</v>
       </c>
-      <c r="B177" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A178" s="3" t="s">
+      <c r="B178" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
         <v>217</v>
       </c>
-      <c r="B178" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A179" s="3" t="s">
+      <c r="B179" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
         <v>218</v>
       </c>
-      <c r="B179" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A180" s="3" t="s">
+      <c r="B180" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
         <v>219</v>
       </c>
-      <c r="B180" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A181" s="3" t="s">
+      <c r="B181" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
         <v>220</v>
       </c>
-      <c r="B181" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A182" s="3" t="s">
+      <c r="B182" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
         <v>221</v>
       </c>
-      <c r="B182" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A183" s="3" t="s">
+      <c r="B183" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
         <v>222</v>
       </c>
-      <c r="B183" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A184" s="3" t="s">
+      <c r="B184" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
         <v>223</v>
       </c>
-      <c r="B184" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A185" s="3" t="s">
+      <c r="B185" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
         <v>224</v>
       </c>
-      <c r="B185" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A186" s="3" t="s">
+      <c r="B186" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
         <v>225</v>
       </c>
-      <c r="B186" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A187" s="3" t="s">
+      <c r="B187" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
         <v>226</v>
       </c>
-      <c r="B187" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A188" s="3" t="s">
+      <c r="B188" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
         <v>227</v>
       </c>
-      <c r="B188" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A189" s="3" t="s">
+      <c r="B189" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
         <v>228</v>
       </c>
-      <c r="B189" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A190" s="3" t="s">
+      <c r="B190" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
         <v>229</v>
       </c>
-      <c r="B190" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A191" s="3" t="s">
+      <c r="B191" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
         <v>230</v>
       </c>
-      <c r="B191" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A192" s="3" t="s">
+      <c r="B192" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
         <v>231</v>
       </c>
-      <c r="B192" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A193" s="3" t="s">
+      <c r="B193" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
         <v>232</v>
       </c>
-      <c r="B193" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A194" s="3" t="s">
+      <c r="B194" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
         <v>233</v>
       </c>
-      <c r="B194" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A195" s="3" t="s">
+      <c r="B195" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
         <v>234</v>
       </c>
-      <c r="B195" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A196" s="3" t="s">
+      <c r="B196" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
         <v>235</v>
       </c>
-      <c r="B196" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A197" s="3" t="s">
+      <c r="B197" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
         <v>236</v>
       </c>
-      <c r="B197" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A198" s="3" t="s">
+      <c r="B198" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
         <v>237</v>
       </c>
-      <c r="B198" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A199" s="3" t="s">
+      <c r="B199" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
         <v>238</v>
       </c>
-      <c r="B199" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A200" s="3" t="s">
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
         <v>239</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A201" s="3" t="s">
-        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/Pyhton Programs.xlsx
+++ b/Pyhton Programs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workplace\Python-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1666E250-68A5-4303-A516-7A43213AB3AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{052E6455-D643-425F-B67E-69FF467917C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
   </bookViews>
   <sheets>
     <sheet name="Python" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="420">
   <si>
     <t>Program NO</t>
   </si>
@@ -1255,13 +1255,162 @@
   </si>
   <si>
     <t>For , While,do_while loop</t>
+  </si>
+  <si>
+    <t>OOP Public access specifiers in python (Non-Static) Instance Variable</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">OOP Protected access specifiers in python (Non-Static) Instance Variable </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ERROR Resolved</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">OOP Protected access specifiers in python (Non-Static) Instance Variable </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ERROR Protected</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">OOP Private access specifiers in python (Non-Static) Instance Variable </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Acessible to Base(Child) Class</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>self._iNO = 11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">OOP Private access specifiers in python (Non-Static) Instance Variable </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NOT Acessible to Base(Child) Class</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>self.__iNO = 21</t>
+    </r>
+  </si>
+  <si>
+    <t>OOP Using All modifers</t>
+  </si>
+  <si>
+    <t>OOP Error Of Private access Speicifer</t>
+  </si>
+  <si>
+    <t>OOP Protected function(Methods) can accsible to object but not good programming practise</t>
+  </si>
+  <si>
+    <t>OOP Protected function(Methods) can accsible from Derived class programming practise</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">OOP Private function Call from Object </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ERROR</t>
+    </r>
+  </si>
+  <si>
+    <t>OOP Private function Call from another public function to private function of same class</t>
+  </si>
+  <si>
+    <t>OOP Overriding the function</t>
+  </si>
+  <si>
+    <t>OOP calling overided function from base class</t>
+  </si>
+  <si>
+    <t>Check Number is Even or Odd</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1278,6 +1427,14 @@
     <font>
       <b/>
       <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -1651,7 +1808,7 @@
   <cols>
     <col min="1" max="1" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="102" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="107.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -2233,6 +2390,9 @@
       <c r="B53" t="s">
         <v>23</v>
       </c>
+      <c r="C53" t="s">
+        <v>406</v>
+      </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
@@ -2241,6 +2401,9 @@
       <c r="B54" t="s">
         <v>23</v>
       </c>
+      <c r="C54" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
@@ -2249,6 +2412,9 @@
       <c r="B55" t="s">
         <v>23</v>
       </c>
+      <c r="C55" t="s">
+        <v>407</v>
+      </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
@@ -2257,6 +2423,9 @@
       <c r="B56" t="s">
         <v>23</v>
       </c>
+      <c r="C56" t="s">
+        <v>412</v>
+      </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
@@ -2265,6 +2434,9 @@
       <c r="B57" t="s">
         <v>23</v>
       </c>
+      <c r="C57" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
@@ -2273,6 +2445,9 @@
       <c r="B58" t="s">
         <v>23</v>
       </c>
+      <c r="C58" t="s">
+        <v>410</v>
+      </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
@@ -2281,6 +2456,9 @@
       <c r="B59" t="s">
         <v>23</v>
       </c>
+      <c r="C59" t="s">
+        <v>411</v>
+      </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
@@ -2289,6 +2467,9 @@
       <c r="B60" t="s">
         <v>23</v>
       </c>
+      <c r="C60" t="s">
+        <v>413</v>
+      </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
@@ -2297,6 +2478,9 @@
       <c r="B61" t="s">
         <v>23</v>
       </c>
+      <c r="C61" t="s">
+        <v>414</v>
+      </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
@@ -2305,6 +2489,9 @@
       <c r="B62" t="s">
         <v>23</v>
       </c>
+      <c r="C62" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
@@ -2313,6 +2500,9 @@
       <c r="B63" t="s">
         <v>23</v>
       </c>
+      <c r="C63" t="s">
+        <v>416</v>
+      </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
@@ -2321,24 +2511,33 @@
       <c r="B64" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C64" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>289</v>
       </c>
       <c r="B65" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C65" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>290</v>
       </c>
       <c r="B66" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C66" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>291</v>
       </c>
@@ -2346,7 +2545,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>292</v>
       </c>
@@ -2354,7 +2553,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>293</v>
       </c>
@@ -2362,7 +2561,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>294</v>
       </c>
@@ -2370,7 +2569,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>295</v>
       </c>
@@ -2378,7 +2577,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>296</v>
       </c>
@@ -2386,7 +2585,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>297</v>
       </c>
@@ -2394,7 +2593,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>298</v>
       </c>
@@ -2402,7 +2601,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>299</v>
       </c>
@@ -2410,7 +2609,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>300</v>
       </c>
@@ -2418,7 +2617,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>301</v>
       </c>
@@ -2426,7 +2625,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>302</v>
       </c>
@@ -2434,7 +2633,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>303</v>
       </c>
@@ -2442,7 +2641,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>304</v>
       </c>

--- a/Pyhton Programs.xlsx
+++ b/Pyhton Programs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workplace\Python-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{052E6455-D643-425F-B67E-69FF467917C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D570F2E4-C13A-47D2-8714-AE14942B2735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="480">
   <si>
     <t>Program NO</t>
   </si>
@@ -1404,6 +1404,252 @@
   </si>
   <si>
     <t>Check Number is Even or Odd</t>
+  </si>
+  <si>
+    <t>Check EvenOdd Function printing in function</t>
+  </si>
+  <si>
+    <t>Check EvenOdd Function returninig remainder</t>
+  </si>
+  <si>
+    <t>Check EvenOdd Function reuturning iReaminder</t>
+  </si>
+  <si>
+    <t>Check EvenOdd Function returnung boolean</t>
+  </si>
+  <si>
+    <t>Check EvenOdd Function returning booleanX</t>
+  </si>
+  <si>
+    <t>Calculate Ticket Price Multiple If and else</t>
+  </si>
+  <si>
+    <t>Calculate Ticket Price Multiple If and else Handling Negative Case Correct Input</t>
+  </si>
+  <si>
+    <t>Calculate Ticket Price Multiple If and else If Negative input Return error</t>
+  </si>
+  <si>
+    <t>Calculate Ticket Price Multiple If and else Returning -1</t>
+  </si>
+  <si>
+    <t>Calculate Ticket Price Multiple If and else Returning -1 Saying user to enter Correct Input</t>
+  </si>
+  <si>
+    <t>Sequence in Python</t>
+  </si>
+  <si>
+    <t>Convering Sequence Code into Iteration</t>
+  </si>
+  <si>
+    <t>Calculate Ticket Price Multiple If and else Range Built in function</t>
+  </si>
+  <si>
+    <t>Importin Math Modeule</t>
+  </si>
+  <si>
+    <t>Program to Put Even and Odd elements in a List into Two Different Lists. Given lists are L= [2,19,24,56,77,59,90,62,46].</t>
+  </si>
+  <si>
+    <t>Python program to obtain the marks in computer of some students and find mean median and mode. The marks are given as 84,95,76,54,96,88,91,92,95,75,91,97,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program to Generate Random Numbers from 1 to 20 and append them to the List. </t>
+  </si>
+  <si>
+    <t>Python program to accept the base and perpendicular and find the hypotenuse of a right-angled triangle.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Program to Find all Numbers in a Range which are Perfect Squares and Sum of 
+all Digits in the Number is Less than 10. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(is_integer(),math.sqrt())</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">using statstics finding mean,median,mode </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(import statistics as stat stat.mean(),stat.median(),stat.mode())</t>
+    </r>
+  </si>
+  <si>
+    <t>Write a Python program to read 2 numbers from user. Display the result using bitwise and, bitwise or, bitwise xor, right shift and left shift operator</t>
+  </si>
+  <si>
+    <r>
+      <t>Program to Remove the Duplicate Items from a List.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Converting List To Set)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Write a python program to check the given date by the user is valid.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Remove Duplicats user defined function)</t>
+    </r>
+  </si>
+  <si>
+    <t>Program to concatenate dictionaries to create a new one.(User Defind Function)</t>
+  </si>
+  <si>
+    <t>Write a python program to find the roots of a quadratic equation. The standard form of quadratic equation is</t>
+  </si>
+  <si>
+    <t>Program to check whether a given key already exists in a dictionary.</t>
+  </si>
+  <si>
+    <t>Python Program to Convert Decimal to Binary, Octal and Hexadecimal using anonymous function.</t>
+  </si>
+  <si>
+    <r>
+      <t>Program to merge two Python dictionaries.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Dic1 | Dic2)</t>
+    </r>
+  </si>
+  <si>
+    <t>WAP to read a 4-digit number through the keyboard and calculate sum of digits.</t>
+  </si>
+  <si>
+    <t>Create a function named count vowels that accepts a string and returns the number of vowels in the string.</t>
+  </si>
+  <si>
+    <t>Program to check if a year is leap year or not. consider century year also.</t>
+  </si>
+  <si>
+    <t>Program to Find the Factorial of a Number Using Recursion.</t>
+  </si>
+  <si>
+    <t>Given a string. Delete from it all the characters whose indices are divisible by 3.</t>
+  </si>
+  <si>
+    <t>Program to Update the first set with items that don’t exist in the second set. Consider any 2 sets.</t>
+  </si>
+  <si>
+    <t>Write a program to reverse 4-digit number using % and // operators.</t>
+  </si>
+  <si>
+    <t>Python Program to Sort Words in Alphabetic Order</t>
+  </si>
+  <si>
+    <t>Sorting Of list by userdefined Function Bubble sort</t>
+  </si>
+  <si>
+    <t>Create a function to calculate square and cube of a number and return Multiple Values from a Function.</t>
+  </si>
+  <si>
+    <t>Function to check if a number is even or odd and return the result to the function</t>
+  </si>
+  <si>
+    <t>WAP which prompts user to enter radius of circle. If the radius is greater than 0 and then calculate and print the area and circumference of the circle.</t>
+  </si>
+  <si>
+    <t>.WAP to test whether a number is divisible by 3 and 15 or by 3 and 15.</t>
+  </si>
+  <si>
+    <t>.WAP to calculate the square of only those numbers whose least significant digit is 5.</t>
+  </si>
+  <si>
+    <t>Write a Python program that reads a text file, counts the number of words in it, and writes the word count to a new file.</t>
+  </si>
+  <si>
+    <t>Write a Python program that reads the content of one text file and writes it to another file.</t>
+  </si>
+  <si>
+    <t>To keep record of patients’ medical data, manipulate files to store, update, and delete such information.</t>
+  </si>
+  <si>
+    <t>Delete a particular word file</t>
+  </si>
+  <si>
+    <t>Delete a particular line from file</t>
+  </si>
+  <si>
+    <t>Enter A data of student and get a data of particulr name by student</t>
+  </si>
+  <si>
+    <t>Function to Find the Sum of the Digits of the Number Recursively.</t>
+  </si>
+  <si>
+    <t>Read the string “hello world” from the user. Make use of continue keyword and remove space</t>
+  </si>
+  <si>
+    <t>Program to check armstromg number or not</t>
+  </si>
+  <si>
+    <t>Printing a pattern of pyramid</t>
+  </si>
+  <si>
+    <t>NUMPY IN PYTHON</t>
+  </si>
+  <si>
+    <t>Addition,Substraction and division in numpy</t>
+  </si>
+  <si>
+    <t>matplotlib in python</t>
+  </si>
+  <si>
+    <t>First n fibnaci serirs</t>
+  </si>
+  <si>
+    <t>Pattern</t>
+  </si>
+  <si>
+    <t>Python Program to Display Powers of 2 Using Anonymous Function</t>
+  </si>
+  <si>
+    <t>.write a function count(word, letter) which takes a word and a letter as arguments and returns the number of occurrences of that letter in the word.</t>
+  </si>
+  <si>
+    <t>Python Program to Find HCF or GCD</t>
   </si>
 </sst>
 </file>
@@ -1461,7 +1707,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1469,6 +1715,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2544,6 +2794,9 @@
       <c r="B67" t="s">
         <v>23</v>
       </c>
+      <c r="C67" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
@@ -2552,6 +2805,9 @@
       <c r="B68" t="s">
         <v>23</v>
       </c>
+      <c r="C68" t="s">
+        <v>421</v>
+      </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
@@ -2560,6 +2816,9 @@
       <c r="B69" t="s">
         <v>23</v>
       </c>
+      <c r="C69" t="s">
+        <v>422</v>
+      </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
@@ -2568,6 +2827,9 @@
       <c r="B70" t="s">
         <v>23</v>
       </c>
+      <c r="C70" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
@@ -2576,6 +2838,9 @@
       <c r="B71" t="s">
         <v>23</v>
       </c>
+      <c r="C71" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
@@ -2584,6 +2849,9 @@
       <c r="B72" t="s">
         <v>23</v>
       </c>
+      <c r="C72" t="s">
+        <v>425</v>
+      </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
@@ -2592,6 +2860,9 @@
       <c r="B73" t="s">
         <v>23</v>
       </c>
+      <c r="C73" t="s">
+        <v>426</v>
+      </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
@@ -2600,6 +2871,9 @@
       <c r="B74" t="s">
         <v>23</v>
       </c>
+      <c r="C74" t="s">
+        <v>427</v>
+      </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
@@ -2608,6 +2882,9 @@
       <c r="B75" t="s">
         <v>23</v>
       </c>
+      <c r="C75" t="s">
+        <v>428</v>
+      </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
@@ -2616,6 +2893,9 @@
       <c r="B76" t="s">
         <v>23</v>
       </c>
+      <c r="C76" t="s">
+        <v>429</v>
+      </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
@@ -2624,6 +2904,9 @@
       <c r="B77" t="s">
         <v>23</v>
       </c>
+      <c r="C77" t="s">
+        <v>430</v>
+      </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
@@ -2632,6 +2915,9 @@
       <c r="B78" t="s">
         <v>23</v>
       </c>
+      <c r="C78" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
@@ -2640,6 +2926,9 @@
       <c r="B79" t="s">
         <v>23</v>
       </c>
+      <c r="C79" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
@@ -2648,280 +2937,385 @@
       <c r="B80" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C80" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>305</v>
       </c>
       <c r="B81" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C81" s="4" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>306</v>
       </c>
       <c r="B82" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C82" s="3" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>307</v>
       </c>
       <c r="B83" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C83" s="4" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>308</v>
       </c>
       <c r="B84" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C84" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>309</v>
       </c>
       <c r="B85" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C85" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>310</v>
       </c>
       <c r="B86" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C86" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>311</v>
       </c>
       <c r="B87" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C87" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>312</v>
       </c>
       <c r="B88" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C88" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>313</v>
       </c>
       <c r="B89" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C89" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>314</v>
       </c>
       <c r="B90" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C90" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>315</v>
       </c>
       <c r="B91" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C91" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>316</v>
       </c>
       <c r="B92" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C92" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>317</v>
       </c>
       <c r="B93" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C93" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>318</v>
       </c>
       <c r="B94" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C94" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>319</v>
       </c>
       <c r="B95" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C95" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>320</v>
       </c>
       <c r="B96" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C96" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>321</v>
       </c>
       <c r="B97" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C97" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>322</v>
       </c>
       <c r="B98" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C98" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>323</v>
       </c>
       <c r="B99" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C99" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>324</v>
       </c>
       <c r="B100" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C100" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>325</v>
       </c>
       <c r="B101" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C101" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>326</v>
       </c>
       <c r="B102" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C102" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>327</v>
       </c>
       <c r="B103" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C103" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>328</v>
       </c>
       <c r="B104" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C104" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>329</v>
       </c>
       <c r="B105" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C105" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>330</v>
       </c>
       <c r="B106" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C106" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>331</v>
       </c>
       <c r="B107" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C107" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>332</v>
       </c>
       <c r="B108" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C108" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>333</v>
       </c>
       <c r="B109" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C109" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>334</v>
       </c>
       <c r="B110" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C110" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>335</v>
       </c>
       <c r="B111" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C111" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>336</v>
       </c>
       <c r="B112" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C112" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>337</v>
       </c>
       <c r="B113" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C113" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>338</v>
       </c>
       <c r="B114" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C114" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>339</v>
       </c>
@@ -2929,103 +3323,139 @@
         <v>23</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>340</v>
       </c>
       <c r="B116" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C116" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>341</v>
       </c>
       <c r="B117" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C117" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>342</v>
       </c>
       <c r="B118" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C118" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>343</v>
       </c>
       <c r="B119" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C119" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>344</v>
       </c>
       <c r="B120" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C120" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>345</v>
       </c>
       <c r="B121" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C121" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>346</v>
       </c>
       <c r="B122" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C122" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>347</v>
       </c>
       <c r="B123" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C123" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>348</v>
       </c>
       <c r="B124" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C124" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>349</v>
       </c>
       <c r="B125" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C125" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>350</v>
       </c>
       <c r="B126" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C126" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>351</v>
       </c>
       <c r="B127" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C127" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>352</v>
       </c>

--- a/Pyhton Programs.xlsx
+++ b/Pyhton Programs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workplace\Python-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D570F2E4-C13A-47D2-8714-AE14942B2735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA84DC82-0CA4-4966-BBE1-812E8FB0747D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
+    <workbookView xWindow="1128" yWindow="1416" windowWidth="18816" windowHeight="11544" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
   </bookViews>
   <sheets>
     <sheet name="Python" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1429" uniqueCount="797">
   <si>
     <t>Program NO</t>
   </si>
@@ -1651,12 +1651,976 @@
   <si>
     <t>Python Program to Find HCF or GCD</t>
   </si>
+  <si>
+    <t>Sum of factor</t>
+  </si>
+  <si>
+    <t>Perfect Number</t>
+  </si>
+  <si>
+    <t>Problem based on number</t>
+  </si>
+  <si>
+    <t>Changing step of range function</t>
+  </si>
+  <si>
+    <t>Display reverse The numbers</t>
+  </si>
+  <si>
+    <t>Negative Reverse the line</t>
+  </si>
+  <si>
+    <t>Number line</t>
+  </si>
+  <si>
+    <t>CheckPrime using Flag</t>
+  </si>
+  <si>
+    <t>CheckPrime without usinf flag</t>
+  </si>
+  <si>
+    <t>CheckPalindrome Using Class</t>
+  </si>
+  <si>
+    <t>Array operation (List)</t>
+  </si>
+  <si>
+    <t>Printing List using for loop</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Size of list Using sys library </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Size of emppty Dictionary is : 56)</t>
+    </r>
+  </si>
+  <si>
+    <t>Printing address of List element</t>
+  </si>
+  <si>
+    <t>Summation of list</t>
+  </si>
+  <si>
+    <t>CountEven in Number in list</t>
+  </si>
+  <si>
+    <t>Sumof Even Number in array</t>
+  </si>
+  <si>
+    <t>Program 144</t>
+  </si>
+  <si>
+    <t>Program 145</t>
+  </si>
+  <si>
+    <t>Program 146</t>
+  </si>
+  <si>
+    <t>Program 147</t>
+  </si>
+  <si>
+    <t>Program 148</t>
+  </si>
+  <si>
+    <t>Program 149</t>
+  </si>
+  <si>
+    <t>Program 150</t>
+  </si>
+  <si>
+    <t>Program 151</t>
+  </si>
+  <si>
+    <t>Program 152</t>
+  </si>
+  <si>
+    <t>Program 153</t>
+  </si>
+  <si>
+    <t>Program 154</t>
+  </si>
+  <si>
+    <t>Program 155</t>
+  </si>
+  <si>
+    <t>Program 156</t>
+  </si>
+  <si>
+    <t>Program 157</t>
+  </si>
+  <si>
+    <t>Program 158</t>
+  </si>
+  <si>
+    <t>Program 159</t>
+  </si>
+  <si>
+    <t>Program 160</t>
+  </si>
+  <si>
+    <t>Program 161</t>
+  </si>
+  <si>
+    <t>Program 162</t>
+  </si>
+  <si>
+    <t>Program 163</t>
+  </si>
+  <si>
+    <t>Program 164</t>
+  </si>
+  <si>
+    <t>Program 165</t>
+  </si>
+  <si>
+    <t>Program 166</t>
+  </si>
+  <si>
+    <t>Program 167</t>
+  </si>
+  <si>
+    <t>Program 168</t>
+  </si>
+  <si>
+    <t>Program 169</t>
+  </si>
+  <si>
+    <t>Program 170</t>
+  </si>
+  <si>
+    <t>Program 171</t>
+  </si>
+  <si>
+    <t>Program 172</t>
+  </si>
+  <si>
+    <t>Program 173</t>
+  </si>
+  <si>
+    <t>Program 174</t>
+  </si>
+  <si>
+    <t>Program 175</t>
+  </si>
+  <si>
+    <t>Program 176</t>
+  </si>
+  <si>
+    <t>Program 177</t>
+  </si>
+  <si>
+    <t>Program 178</t>
+  </si>
+  <si>
+    <t>Program 179</t>
+  </si>
+  <si>
+    <t>Program 180</t>
+  </si>
+  <si>
+    <t>Program 181</t>
+  </si>
+  <si>
+    <t>Program 182</t>
+  </si>
+  <si>
+    <t>Program 183</t>
+  </si>
+  <si>
+    <t>Program 184</t>
+  </si>
+  <si>
+    <t>Program 185</t>
+  </si>
+  <si>
+    <t>Program 186</t>
+  </si>
+  <si>
+    <t>Program 187</t>
+  </si>
+  <si>
+    <t>Program 188</t>
+  </si>
+  <si>
+    <t>Program 189</t>
+  </si>
+  <si>
+    <t>Program 190</t>
+  </si>
+  <si>
+    <t>Program 191</t>
+  </si>
+  <si>
+    <t>Program 192</t>
+  </si>
+  <si>
+    <t>Program 193</t>
+  </si>
+  <si>
+    <t>Program 194</t>
+  </si>
+  <si>
+    <t>Program 195</t>
+  </si>
+  <si>
+    <t>Program 196</t>
+  </si>
+  <si>
+    <t>Program 197</t>
+  </si>
+  <si>
+    <t>Program 198</t>
+  </si>
+  <si>
+    <t>Program 199</t>
+  </si>
+  <si>
+    <t>Program 200</t>
+  </si>
+  <si>
+    <t>Program 201</t>
+  </si>
+  <si>
+    <t>Program 202</t>
+  </si>
+  <si>
+    <t>Program 203</t>
+  </si>
+  <si>
+    <t>Program 204</t>
+  </si>
+  <si>
+    <t>Program 205</t>
+  </si>
+  <si>
+    <t>Program 206</t>
+  </si>
+  <si>
+    <t>Program 207</t>
+  </si>
+  <si>
+    <t>Program 208</t>
+  </si>
+  <si>
+    <t>Program 209</t>
+  </si>
+  <si>
+    <t>Program 210</t>
+  </si>
+  <si>
+    <t>Program 211</t>
+  </si>
+  <si>
+    <t>Program 212</t>
+  </si>
+  <si>
+    <t>Program 213</t>
+  </si>
+  <si>
+    <t>Program 214</t>
+  </si>
+  <si>
+    <t>Program 215</t>
+  </si>
+  <si>
+    <t>Program 216</t>
+  </si>
+  <si>
+    <t>Program 217</t>
+  </si>
+  <si>
+    <t>Program 218</t>
+  </si>
+  <si>
+    <t>Program 219</t>
+  </si>
+  <si>
+    <t>Program 220</t>
+  </si>
+  <si>
+    <t>Program 221</t>
+  </si>
+  <si>
+    <t>Program 222</t>
+  </si>
+  <si>
+    <t>Program 223</t>
+  </si>
+  <si>
+    <t>Program 224</t>
+  </si>
+  <si>
+    <t>Program 225</t>
+  </si>
+  <si>
+    <t>Program 226</t>
+  </si>
+  <si>
+    <t>Program 227</t>
+  </si>
+  <si>
+    <t>Program 228</t>
+  </si>
+  <si>
+    <t>Program 229</t>
+  </si>
+  <si>
+    <t>Program 230</t>
+  </si>
+  <si>
+    <t>Program 231</t>
+  </si>
+  <si>
+    <t>Program 232</t>
+  </si>
+  <si>
+    <t>Program 233</t>
+  </si>
+  <si>
+    <t>Program 234</t>
+  </si>
+  <si>
+    <t>Program 235</t>
+  </si>
+  <si>
+    <t>Program 236</t>
+  </si>
+  <si>
+    <t>Program 237</t>
+  </si>
+  <si>
+    <t>Program 238</t>
+  </si>
+  <si>
+    <t>Program 239</t>
+  </si>
+  <si>
+    <t>Program 240</t>
+  </si>
+  <si>
+    <t>Program 241</t>
+  </si>
+  <si>
+    <t>Program 242</t>
+  </si>
+  <si>
+    <t>Program 243</t>
+  </si>
+  <si>
+    <t>Program 244</t>
+  </si>
+  <si>
+    <t>Program 245</t>
+  </si>
+  <si>
+    <t>Program 246</t>
+  </si>
+  <si>
+    <t>Program 247</t>
+  </si>
+  <si>
+    <t>Program 248</t>
+  </si>
+  <si>
+    <t>Program 249</t>
+  </si>
+  <si>
+    <t>Program 250</t>
+  </si>
+  <si>
+    <t>Program 251</t>
+  </si>
+  <si>
+    <t>Program 252</t>
+  </si>
+  <si>
+    <t>Program 253</t>
+  </si>
+  <si>
+    <t>Program 254</t>
+  </si>
+  <si>
+    <t>Program 255</t>
+  </si>
+  <si>
+    <t>Program 256</t>
+  </si>
+  <si>
+    <t>Program 257</t>
+  </si>
+  <si>
+    <t>Program 258</t>
+  </si>
+  <si>
+    <t>Program 259</t>
+  </si>
+  <si>
+    <t>Program 260</t>
+  </si>
+  <si>
+    <t>Program 261</t>
+  </si>
+  <si>
+    <t>Program 262</t>
+  </si>
+  <si>
+    <t>Program 263</t>
+  </si>
+  <si>
+    <t>Program 264</t>
+  </si>
+  <si>
+    <t>Program 265</t>
+  </si>
+  <si>
+    <t>Program 266</t>
+  </si>
+  <si>
+    <t>Program 267</t>
+  </si>
+  <si>
+    <t>Program 268</t>
+  </si>
+  <si>
+    <t>Program 269</t>
+  </si>
+  <si>
+    <t>Program 270</t>
+  </si>
+  <si>
+    <t>Program 271</t>
+  </si>
+  <si>
+    <t>Program 272</t>
+  </si>
+  <si>
+    <t>Program 273</t>
+  </si>
+  <si>
+    <t>Program 274</t>
+  </si>
+  <si>
+    <t>Program 275</t>
+  </si>
+  <si>
+    <t>Program 276</t>
+  </si>
+  <si>
+    <t>Program 277</t>
+  </si>
+  <si>
+    <t>Program 278</t>
+  </si>
+  <si>
+    <t>Program 279</t>
+  </si>
+  <si>
+    <t>Program 280</t>
+  </si>
+  <si>
+    <t>Program 281</t>
+  </si>
+  <si>
+    <t>Program 282</t>
+  </si>
+  <si>
+    <t>Program 283</t>
+  </si>
+  <si>
+    <t>Program 284</t>
+  </si>
+  <si>
+    <t>Program 285</t>
+  </si>
+  <si>
+    <t>Program 286</t>
+  </si>
+  <si>
+    <t>Program 287</t>
+  </si>
+  <si>
+    <t>Program 288</t>
+  </si>
+  <si>
+    <t>Program 289</t>
+  </si>
+  <si>
+    <t>Program 290</t>
+  </si>
+  <si>
+    <t>Program 291</t>
+  </si>
+  <si>
+    <t>Program 292</t>
+  </si>
+  <si>
+    <t>Program 293</t>
+  </si>
+  <si>
+    <t>Program 294</t>
+  </si>
+  <si>
+    <t>Program 295</t>
+  </si>
+  <si>
+    <t>Program 296</t>
+  </si>
+  <si>
+    <t>Program 297</t>
+  </si>
+  <si>
+    <t>Program 298</t>
+  </si>
+  <si>
+    <t>Program 299</t>
+  </si>
+  <si>
+    <t>Program 300</t>
+  </si>
+  <si>
+    <t>Program 301</t>
+  </si>
+  <si>
+    <t>Program 302</t>
+  </si>
+  <si>
+    <t>Program 303</t>
+  </si>
+  <si>
+    <t>Program 304</t>
+  </si>
+  <si>
+    <t>Program 305</t>
+  </si>
+  <si>
+    <t>Program 306</t>
+  </si>
+  <si>
+    <t>Program 307</t>
+  </si>
+  <si>
+    <t>Program 308</t>
+  </si>
+  <si>
+    <t>Program 309</t>
+  </si>
+  <si>
+    <t>Program 310</t>
+  </si>
+  <si>
+    <t>Program 311</t>
+  </si>
+  <si>
+    <t>Program 312</t>
+  </si>
+  <si>
+    <t>Program 313</t>
+  </si>
+  <si>
+    <t>Program 314</t>
+  </si>
+  <si>
+    <t>Program 315</t>
+  </si>
+  <si>
+    <t>Program 316</t>
+  </si>
+  <si>
+    <t>Program 317</t>
+  </si>
+  <si>
+    <t>Program 318</t>
+  </si>
+  <si>
+    <t>Program 319</t>
+  </si>
+  <si>
+    <t>Program 320</t>
+  </si>
+  <si>
+    <t>Program 321</t>
+  </si>
+  <si>
+    <t>Program 322</t>
+  </si>
+  <si>
+    <t>Program 323</t>
+  </si>
+  <si>
+    <t>Program 324</t>
+  </si>
+  <si>
+    <t>Program 325</t>
+  </si>
+  <si>
+    <t>Program 326</t>
+  </si>
+  <si>
+    <t>Program 327</t>
+  </si>
+  <si>
+    <t>Program 328</t>
+  </si>
+  <si>
+    <t>Program 329</t>
+  </si>
+  <si>
+    <t>Program 330</t>
+  </si>
+  <si>
+    <t>Program 331</t>
+  </si>
+  <si>
+    <t>Program 332</t>
+  </si>
+  <si>
+    <t>Program 333</t>
+  </si>
+  <si>
+    <t>Program 334</t>
+  </si>
+  <si>
+    <t>Program 335</t>
+  </si>
+  <si>
+    <t>Program 336</t>
+  </si>
+  <si>
+    <t>Program 337</t>
+  </si>
+  <si>
+    <t>Program 338</t>
+  </si>
+  <si>
+    <t>Program 339</t>
+  </si>
+  <si>
+    <t>Program 340</t>
+  </si>
+  <si>
+    <t>Program 341</t>
+  </si>
+  <si>
+    <t>Program 342</t>
+  </si>
+  <si>
+    <t>Program 343</t>
+  </si>
+  <si>
+    <t>Program 344</t>
+  </si>
+  <si>
+    <t>Program 345</t>
+  </si>
+  <si>
+    <t>Program 346</t>
+  </si>
+  <si>
+    <t>Program 347</t>
+  </si>
+  <si>
+    <t>Program 348</t>
+  </si>
+  <si>
+    <t>Program 349</t>
+  </si>
+  <si>
+    <t>Program 350</t>
+  </si>
+  <si>
+    <t>Program 351</t>
+  </si>
+  <si>
+    <t>Program 352</t>
+  </si>
+  <si>
+    <t>Program 353</t>
+  </si>
+  <si>
+    <t>Program 354</t>
+  </si>
+  <si>
+    <t>Program 355</t>
+  </si>
+  <si>
+    <t>Program 356</t>
+  </si>
+  <si>
+    <t>Program 357</t>
+  </si>
+  <si>
+    <t>Program 358</t>
+  </si>
+  <si>
+    <t>Program 359</t>
+  </si>
+  <si>
+    <t>Program 360</t>
+  </si>
+  <si>
+    <t>Program 361</t>
+  </si>
+  <si>
+    <t>Program 362</t>
+  </si>
+  <si>
+    <t>Program 363</t>
+  </si>
+  <si>
+    <t>Program 364</t>
+  </si>
+  <si>
+    <t>Program 365</t>
+  </si>
+  <si>
+    <t>Program 366</t>
+  </si>
+  <si>
+    <t>Program 367</t>
+  </si>
+  <si>
+    <t>Program 368</t>
+  </si>
+  <si>
+    <t>Program 369</t>
+  </si>
+  <si>
+    <t>Program 370</t>
+  </si>
+  <si>
+    <t>Program 371</t>
+  </si>
+  <si>
+    <t>Program 372</t>
+  </si>
+  <si>
+    <t>Program 373</t>
+  </si>
+  <si>
+    <t>Program 374</t>
+  </si>
+  <si>
+    <t>Program 375</t>
+  </si>
+  <si>
+    <t>Program 376</t>
+  </si>
+  <si>
+    <t>Program 377</t>
+  </si>
+  <si>
+    <t>Program 378</t>
+  </si>
+  <si>
+    <t>Program 379</t>
+  </si>
+  <si>
+    <t>Program 380</t>
+  </si>
+  <si>
+    <t>Program 381</t>
+  </si>
+  <si>
+    <t>Program 382</t>
+  </si>
+  <si>
+    <t>Program 383</t>
+  </si>
+  <si>
+    <t>Program 384</t>
+  </si>
+  <si>
+    <t>Program 385</t>
+  </si>
+  <si>
+    <t>Program 386</t>
+  </si>
+  <si>
+    <t>Program 387</t>
+  </si>
+  <si>
+    <t>Program 388</t>
+  </si>
+  <si>
+    <t>Program 389</t>
+  </si>
+  <si>
+    <t>Program 390</t>
+  </si>
+  <si>
+    <t>Program 391</t>
+  </si>
+  <si>
+    <t>Program 392</t>
+  </si>
+  <si>
+    <t>Program 393</t>
+  </si>
+  <si>
+    <t>Program 394</t>
+  </si>
+  <si>
+    <t>Program 395</t>
+  </si>
+  <si>
+    <t>Program 396</t>
+  </si>
+  <si>
+    <t>Program 397</t>
+  </si>
+  <si>
+    <t>Program 398</t>
+  </si>
+  <si>
+    <t>Program 399</t>
+  </si>
+  <si>
+    <t>Program 400</t>
+  </si>
+  <si>
+    <t>Program 401</t>
+  </si>
+  <si>
+    <t>Program 402</t>
+  </si>
+  <si>
+    <t>Program 403</t>
+  </si>
+  <si>
+    <t>Program 404</t>
+  </si>
+  <si>
+    <t>Program 405</t>
+  </si>
+  <si>
+    <t>Program 406</t>
+  </si>
+  <si>
+    <t>Program 407</t>
+  </si>
+  <si>
+    <t>Program 408</t>
+  </si>
+  <si>
+    <t>Program 409</t>
+  </si>
+  <si>
+    <t>Program 410</t>
+  </si>
+  <si>
+    <t>Program 411</t>
+  </si>
+  <si>
+    <t>Program 412</t>
+  </si>
+  <si>
+    <t>Program 413</t>
+  </si>
+  <si>
+    <t>Program 414</t>
+  </si>
+  <si>
+    <t>Program 415</t>
+  </si>
+  <si>
+    <t>Program 416</t>
+  </si>
+  <si>
+    <t>Program 417</t>
+  </si>
+  <si>
+    <t>Program 418</t>
+  </si>
+  <si>
+    <t>Program 419</t>
+  </si>
+  <si>
+    <t>Program 420</t>
+  </si>
+  <si>
+    <t>Program 421</t>
+  </si>
+  <si>
+    <t>Program 422</t>
+  </si>
+  <si>
+    <t>Program 423</t>
+  </si>
+  <si>
+    <t>Program 424</t>
+  </si>
+  <si>
+    <t>Program 425</t>
+  </si>
+  <si>
+    <t>Program 426</t>
+  </si>
+  <si>
+    <t>Program 427</t>
+  </si>
+  <si>
+    <t>Program 428</t>
+  </si>
+  <si>
+    <t>Program 429</t>
+  </si>
+  <si>
+    <t>Program 430</t>
+  </si>
+  <si>
+    <t>Count Of Odd Number in list</t>
+  </si>
+  <si>
+    <t>Linearsearch Using flag</t>
+  </si>
+  <si>
+    <t>Linearsearch Without using flag Using flag</t>
+  </si>
+  <si>
+    <t>Linearsearh using counter compairing length of list and counuter count</t>
+  </si>
+  <si>
+    <t>Maximum in list</t>
+  </si>
+  <si>
+    <t>Minimum Number inlist</t>
+  </si>
+  <si>
+    <t>Update the List At Looping</t>
+  </si>
+  <si>
+    <t>Creating array of own class and object</t>
+  </si>
+  <si>
+    <t>Creating array of own class and object  New Method added</t>
+  </si>
+  <si>
+    <t>1       *       2       *       3       *       4       *       5       *</t>
+  </si>
+  <si>
+    <t>*       #       *       #       *       #       *       #</t>
+  </si>
+  <si>
+    <t>*1*     *2*     *3*     *4*</t>
+  </si>
+  <si>
+    <t>1       *       3       *       5       *</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1685,6 +2649,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1718,7 +2688,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2053,7 +3025,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19D1B62-8AB4-4DE6-A4B9-DCFE9C1F8102}">
-  <dimension ref="A1:C145"/>
+  <dimension ref="A1:C432"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.77734375" bestFit="1" customWidth="1"/>
@@ -2948,7 +3920,7 @@
       <c r="B81" t="s">
         <v>23</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="C81" t="s">
         <v>434</v>
       </c>
     </row>
@@ -2970,7 +3942,7 @@
       <c r="B83" t="s">
         <v>23</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="C83" t="s">
         <v>436</v>
       </c>
     </row>
@@ -3462,140 +4434,2529 @@
       <c r="B128" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C128" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>353</v>
       </c>
       <c r="B129" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C129" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>354</v>
       </c>
       <c r="B130" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C130" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>355</v>
       </c>
       <c r="B131" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C131" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>356</v>
       </c>
       <c r="B132" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C132" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>357</v>
       </c>
       <c r="B133" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C133" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>358</v>
       </c>
       <c r="B134" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C134" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>359</v>
       </c>
       <c r="B135" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C135" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>360</v>
       </c>
       <c r="B136" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C136" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>361</v>
       </c>
       <c r="B137" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C137" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>362</v>
       </c>
       <c r="B138" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C138" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>363</v>
       </c>
       <c r="B139" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C139" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>364</v>
       </c>
       <c r="B140" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C140" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>365</v>
       </c>
       <c r="B141" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C141" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>366</v>
       </c>
       <c r="B142" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C142" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>367</v>
       </c>
       <c r="B143" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C143" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>368</v>
       </c>
       <c r="B144" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C144" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>369</v>
       </c>
       <c r="B145" t="s">
+        <v>23</v>
+      </c>
+      <c r="C145" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>497</v>
+      </c>
+      <c r="B146" t="s">
+        <v>23</v>
+      </c>
+      <c r="C146" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>498</v>
+      </c>
+      <c r="B147" t="s">
+        <v>23</v>
+      </c>
+      <c r="C147" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>499</v>
+      </c>
+      <c r="B148" t="s">
+        <v>23</v>
+      </c>
+      <c r="C148" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>500</v>
+      </c>
+      <c r="B149" t="s">
+        <v>23</v>
+      </c>
+      <c r="C149" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>501</v>
+      </c>
+      <c r="B150" t="s">
+        <v>23</v>
+      </c>
+      <c r="C150" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>502</v>
+      </c>
+      <c r="B151" t="s">
+        <v>23</v>
+      </c>
+      <c r="C151" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>503</v>
+      </c>
+      <c r="B152" t="s">
+        <v>23</v>
+      </c>
+      <c r="C152" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>504</v>
+      </c>
+      <c r="B153" t="s">
+        <v>23</v>
+      </c>
+      <c r="C153" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>505</v>
+      </c>
+      <c r="B154" t="s">
+        <v>23</v>
+      </c>
+      <c r="C154" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>506</v>
+      </c>
+      <c r="B155" t="s">
+        <v>23</v>
+      </c>
+      <c r="C155" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>507</v>
+      </c>
+      <c r="B156" t="s">
+        <v>23</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>508</v>
+      </c>
+      <c r="B157" t="s">
+        <v>23</v>
+      </c>
+      <c r="C157" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>509</v>
+      </c>
+      <c r="B158" t="s">
+        <v>23</v>
+      </c>
+      <c r="C158" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>510</v>
+      </c>
+      <c r="B159" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>511</v>
+      </c>
+      <c r="B160" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>512</v>
+      </c>
+      <c r="B161" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>513</v>
+      </c>
+      <c r="B162" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>514</v>
+      </c>
+      <c r="B163" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>515</v>
+      </c>
+      <c r="B164" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>516</v>
+      </c>
+      <c r="B165" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>517</v>
+      </c>
+      <c r="B166" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>518</v>
+      </c>
+      <c r="B167" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>519</v>
+      </c>
+      <c r="B168" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>520</v>
+      </c>
+      <c r="B169" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>521</v>
+      </c>
+      <c r="B170" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>522</v>
+      </c>
+      <c r="B171" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>523</v>
+      </c>
+      <c r="B172" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>524</v>
+      </c>
+      <c r="B173" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>525</v>
+      </c>
+      <c r="B174" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>526</v>
+      </c>
+      <c r="B175" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>527</v>
+      </c>
+      <c r="B176" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>528</v>
+      </c>
+      <c r="B177" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>529</v>
+      </c>
+      <c r="B178" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>530</v>
+      </c>
+      <c r="B179" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>531</v>
+      </c>
+      <c r="B180" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>532</v>
+      </c>
+      <c r="B181" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>533</v>
+      </c>
+      <c r="B182" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>534</v>
+      </c>
+      <c r="B183" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>535</v>
+      </c>
+      <c r="B184" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>536</v>
+      </c>
+      <c r="B185" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>537</v>
+      </c>
+      <c r="B186" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>538</v>
+      </c>
+      <c r="B187" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>539</v>
+      </c>
+      <c r="B188" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>540</v>
+      </c>
+      <c r="B189" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>541</v>
+      </c>
+      <c r="B190" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>542</v>
+      </c>
+      <c r="B191" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>543</v>
+      </c>
+      <c r="B192" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>544</v>
+      </c>
+      <c r="B193" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>545</v>
+      </c>
+      <c r="B194" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>546</v>
+      </c>
+      <c r="B195" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>547</v>
+      </c>
+      <c r="B196" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>548</v>
+      </c>
+      <c r="B197" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>549</v>
+      </c>
+      <c r="B198" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>550</v>
+      </c>
+      <c r="B199" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>551</v>
+      </c>
+      <c r="B200" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>552</v>
+      </c>
+      <c r="B201" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>553</v>
+      </c>
+      <c r="B202" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>554</v>
+      </c>
+      <c r="B203" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>555</v>
+      </c>
+      <c r="B204" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>556</v>
+      </c>
+      <c r="B205" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>557</v>
+      </c>
+      <c r="B206" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>558</v>
+      </c>
+      <c r="B207" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>559</v>
+      </c>
+      <c r="B208" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>560</v>
+      </c>
+      <c r="B209" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>561</v>
+      </c>
+      <c r="B210" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>562</v>
+      </c>
+      <c r="B211" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>563</v>
+      </c>
+      <c r="B212" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>564</v>
+      </c>
+      <c r="B213" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>565</v>
+      </c>
+      <c r="B214" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>566</v>
+      </c>
+      <c r="B215" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>567</v>
+      </c>
+      <c r="B216" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>568</v>
+      </c>
+      <c r="B217" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>569</v>
+      </c>
+      <c r="B218" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>570</v>
+      </c>
+      <c r="B219" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>571</v>
+      </c>
+      <c r="B220" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>572</v>
+      </c>
+      <c r="B221" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>573</v>
+      </c>
+      <c r="B222" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>574</v>
+      </c>
+      <c r="B223" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>575</v>
+      </c>
+      <c r="B224" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>576</v>
+      </c>
+      <c r="B225" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>577</v>
+      </c>
+      <c r="B226" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>578</v>
+      </c>
+      <c r="B227" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
+        <v>579</v>
+      </c>
+      <c r="B228" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>580</v>
+      </c>
+      <c r="B229" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>581</v>
+      </c>
+      <c r="B230" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>582</v>
+      </c>
+      <c r="B231" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>583</v>
+      </c>
+      <c r="B232" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>584</v>
+      </c>
+      <c r="B233" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>585</v>
+      </c>
+      <c r="B234" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>586</v>
+      </c>
+      <c r="B235" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>587</v>
+      </c>
+      <c r="B236" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>588</v>
+      </c>
+      <c r="B237" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>589</v>
+      </c>
+      <c r="B238" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
+        <v>590</v>
+      </c>
+      <c r="B239" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A240" t="s">
+        <v>591</v>
+      </c>
+      <c r="B240" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
+        <v>592</v>
+      </c>
+      <c r="B241" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A242" t="s">
+        <v>593</v>
+      </c>
+      <c r="B242" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A243" t="s">
+        <v>594</v>
+      </c>
+      <c r="B243" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A244" t="s">
+        <v>595</v>
+      </c>
+      <c r="B244" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>596</v>
+      </c>
+      <c r="B245" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
+        <v>597</v>
+      </c>
+      <c r="B246" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A247" t="s">
+        <v>598</v>
+      </c>
+      <c r="B247" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
+        <v>599</v>
+      </c>
+      <c r="B248" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>600</v>
+      </c>
+      <c r="B249" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>601</v>
+      </c>
+      <c r="B250" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>602</v>
+      </c>
+      <c r="B251" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
+        <v>603</v>
+      </c>
+      <c r="B252" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
+        <v>604</v>
+      </c>
+      <c r="B253" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A254" t="s">
+        <v>605</v>
+      </c>
+      <c r="B254" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A255" t="s">
+        <v>606</v>
+      </c>
+      <c r="B255" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
+        <v>607</v>
+      </c>
+      <c r="B256" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A257" t="s">
+        <v>608</v>
+      </c>
+      <c r="B257" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A258" t="s">
+        <v>609</v>
+      </c>
+      <c r="B258" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>610</v>
+      </c>
+      <c r="B259" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A260" t="s">
+        <v>611</v>
+      </c>
+      <c r="B260" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
+        <v>612</v>
+      </c>
+      <c r="B261" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
+        <v>613</v>
+      </c>
+      <c r="B262" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A263" t="s">
+        <v>614</v>
+      </c>
+      <c r="B263" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A264" t="s">
+        <v>615</v>
+      </c>
+      <c r="B264" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A265" t="s">
+        <v>616</v>
+      </c>
+      <c r="B265" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A266" t="s">
+        <v>617</v>
+      </c>
+      <c r="B266" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A267" t="s">
+        <v>618</v>
+      </c>
+      <c r="B267" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A268" t="s">
+        <v>619</v>
+      </c>
+      <c r="B268" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A269" t="s">
+        <v>620</v>
+      </c>
+      <c r="B269" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A270" t="s">
+        <v>621</v>
+      </c>
+      <c r="B270" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A271" t="s">
+        <v>622</v>
+      </c>
+      <c r="B271" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A272" t="s">
+        <v>623</v>
+      </c>
+      <c r="B272" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>624</v>
+      </c>
+      <c r="B273" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>625</v>
+      </c>
+      <c r="B274" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>626</v>
+      </c>
+      <c r="B275" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>627</v>
+      </c>
+      <c r="B276" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>628</v>
+      </c>
+      <c r="B277" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>629</v>
+      </c>
+      <c r="B278" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A279" t="s">
+        <v>630</v>
+      </c>
+      <c r="B279" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A280" t="s">
+        <v>631</v>
+      </c>
+      <c r="B280" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A281" t="s">
+        <v>632</v>
+      </c>
+      <c r="B281" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>633</v>
+      </c>
+      <c r="B282" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
+        <v>634</v>
+      </c>
+      <c r="B283" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>635</v>
+      </c>
+      <c r="B284" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>636</v>
+      </c>
+      <c r="B285" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>637</v>
+      </c>
+      <c r="B286" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A287" t="s">
+        <v>638</v>
+      </c>
+      <c r="B287" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A288" t="s">
+        <v>639</v>
+      </c>
+      <c r="B288" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A289" t="s">
+        <v>640</v>
+      </c>
+      <c r="B289" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A290" t="s">
+        <v>641</v>
+      </c>
+      <c r="B290" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A291" t="s">
+        <v>642</v>
+      </c>
+      <c r="B291" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A292" t="s">
+        <v>643</v>
+      </c>
+      <c r="B292" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A293" t="s">
+        <v>644</v>
+      </c>
+      <c r="B293" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A294" t="s">
+        <v>645</v>
+      </c>
+      <c r="B294" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A295" t="s">
+        <v>646</v>
+      </c>
+      <c r="B295" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A296" t="s">
+        <v>647</v>
+      </c>
+      <c r="B296" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A297" t="s">
+        <v>648</v>
+      </c>
+      <c r="B297" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A298" t="s">
+        <v>649</v>
+      </c>
+      <c r="B298" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A299" t="s">
+        <v>650</v>
+      </c>
+      <c r="B299" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A300" t="s">
+        <v>651</v>
+      </c>
+      <c r="B300" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A301" t="s">
+        <v>652</v>
+      </c>
+      <c r="B301" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A302" t="s">
+        <v>653</v>
+      </c>
+      <c r="B302" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A303" t="s">
+        <v>654</v>
+      </c>
+      <c r="B303" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A304" t="s">
+        <v>655</v>
+      </c>
+      <c r="B304" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A305" t="s">
+        <v>656</v>
+      </c>
+      <c r="B305" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A306" t="s">
+        <v>657</v>
+      </c>
+      <c r="B306" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A307" t="s">
+        <v>658</v>
+      </c>
+      <c r="B307" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A308" t="s">
+        <v>659</v>
+      </c>
+      <c r="B308" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A309" t="s">
+        <v>660</v>
+      </c>
+      <c r="B309" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A310" t="s">
+        <v>661</v>
+      </c>
+      <c r="B310" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A311" t="s">
+        <v>662</v>
+      </c>
+      <c r="B311" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A312" t="s">
+        <v>663</v>
+      </c>
+      <c r="B312" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A313" t="s">
+        <v>664</v>
+      </c>
+      <c r="B313" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A314" t="s">
+        <v>665</v>
+      </c>
+      <c r="B314" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A315" t="s">
+        <v>666</v>
+      </c>
+      <c r="B315" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A316" t="s">
+        <v>667</v>
+      </c>
+      <c r="B316" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A317" t="s">
+        <v>668</v>
+      </c>
+      <c r="B317" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A318" t="s">
+        <v>669</v>
+      </c>
+      <c r="B318" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A319" t="s">
+        <v>670</v>
+      </c>
+      <c r="B319" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A320" t="s">
+        <v>671</v>
+      </c>
+      <c r="B320" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A321" t="s">
+        <v>672</v>
+      </c>
+      <c r="B321" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A322" t="s">
+        <v>673</v>
+      </c>
+      <c r="B322" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A323" t="s">
+        <v>674</v>
+      </c>
+      <c r="B323" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A324" t="s">
+        <v>675</v>
+      </c>
+      <c r="B324" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A325" t="s">
+        <v>676</v>
+      </c>
+      <c r="B325" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A326" t="s">
+        <v>677</v>
+      </c>
+      <c r="B326" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A327" t="s">
+        <v>678</v>
+      </c>
+      <c r="B327" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A328" t="s">
+        <v>679</v>
+      </c>
+      <c r="B328" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A329" t="s">
+        <v>680</v>
+      </c>
+      <c r="B329" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A330" t="s">
+        <v>681</v>
+      </c>
+      <c r="B330" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A331" t="s">
+        <v>682</v>
+      </c>
+      <c r="B331" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A332" t="s">
+        <v>683</v>
+      </c>
+      <c r="B332" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A333" t="s">
+        <v>684</v>
+      </c>
+      <c r="B333" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A334" t="s">
+        <v>685</v>
+      </c>
+      <c r="B334" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A335" t="s">
+        <v>686</v>
+      </c>
+      <c r="B335" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A336" t="s">
+        <v>687</v>
+      </c>
+      <c r="B336" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A337" t="s">
+        <v>688</v>
+      </c>
+      <c r="B337" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A338" t="s">
+        <v>689</v>
+      </c>
+      <c r="B338" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A339" t="s">
+        <v>690</v>
+      </c>
+      <c r="B339" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A340" t="s">
+        <v>691</v>
+      </c>
+      <c r="B340" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A341" t="s">
+        <v>692</v>
+      </c>
+      <c r="B341" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A342" t="s">
+        <v>693</v>
+      </c>
+      <c r="B342" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A343" t="s">
+        <v>694</v>
+      </c>
+      <c r="B343" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A344" t="s">
+        <v>695</v>
+      </c>
+      <c r="B344" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A345" t="s">
+        <v>696</v>
+      </c>
+      <c r="B345" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A346" t="s">
+        <v>697</v>
+      </c>
+      <c r="B346" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A347" t="s">
+        <v>698</v>
+      </c>
+      <c r="B347" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A348" t="s">
+        <v>699</v>
+      </c>
+      <c r="B348" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A349" t="s">
+        <v>700</v>
+      </c>
+      <c r="B349" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A350" t="s">
+        <v>701</v>
+      </c>
+      <c r="B350" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A351" t="s">
+        <v>702</v>
+      </c>
+      <c r="B351" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A352" t="s">
+        <v>703</v>
+      </c>
+      <c r="B352" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A353" t="s">
+        <v>704</v>
+      </c>
+      <c r="B353" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A354" t="s">
+        <v>705</v>
+      </c>
+      <c r="B354" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A355" t="s">
+        <v>706</v>
+      </c>
+      <c r="B355" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A356" t="s">
+        <v>707</v>
+      </c>
+      <c r="B356" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A357" t="s">
+        <v>708</v>
+      </c>
+      <c r="B357" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A358" t="s">
+        <v>709</v>
+      </c>
+      <c r="B358" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A359" t="s">
+        <v>710</v>
+      </c>
+      <c r="B359" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A360" t="s">
+        <v>711</v>
+      </c>
+      <c r="B360" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A361" t="s">
+        <v>712</v>
+      </c>
+      <c r="B361" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A362" t="s">
+        <v>713</v>
+      </c>
+      <c r="B362" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A363" t="s">
+        <v>714</v>
+      </c>
+      <c r="B363" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A364" t="s">
+        <v>715</v>
+      </c>
+      <c r="B364" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A365" t="s">
+        <v>716</v>
+      </c>
+      <c r="B365" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A366" t="s">
+        <v>717</v>
+      </c>
+      <c r="B366" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A367" t="s">
+        <v>718</v>
+      </c>
+      <c r="B367" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A368" t="s">
+        <v>719</v>
+      </c>
+      <c r="B368" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A369" t="s">
+        <v>720</v>
+      </c>
+      <c r="B369" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A370" t="s">
+        <v>721</v>
+      </c>
+      <c r="B370" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A371" t="s">
+        <v>722</v>
+      </c>
+      <c r="B371" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A372" t="s">
+        <v>723</v>
+      </c>
+      <c r="B372" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A373" t="s">
+        <v>724</v>
+      </c>
+      <c r="B373" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A374" t="s">
+        <v>725</v>
+      </c>
+      <c r="B374" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A375" t="s">
+        <v>726</v>
+      </c>
+      <c r="B375" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A376" t="s">
+        <v>727</v>
+      </c>
+      <c r="B376" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A377" t="s">
+        <v>728</v>
+      </c>
+      <c r="B377" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A378" t="s">
+        <v>729</v>
+      </c>
+      <c r="B378" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A379" t="s">
+        <v>730</v>
+      </c>
+      <c r="B379" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A380" t="s">
+        <v>731</v>
+      </c>
+      <c r="B380" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A381" t="s">
+        <v>732</v>
+      </c>
+      <c r="B381" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A382" t="s">
+        <v>733</v>
+      </c>
+      <c r="B382" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A383" t="s">
+        <v>734</v>
+      </c>
+      <c r="B383" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A384" t="s">
+        <v>735</v>
+      </c>
+      <c r="B384" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A385" t="s">
+        <v>736</v>
+      </c>
+      <c r="B385" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A386" t="s">
+        <v>737</v>
+      </c>
+      <c r="B386" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A387" t="s">
+        <v>738</v>
+      </c>
+      <c r="B387" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A388" t="s">
+        <v>739</v>
+      </c>
+      <c r="B388" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A389" t="s">
+        <v>740</v>
+      </c>
+      <c r="B389" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A390" t="s">
+        <v>741</v>
+      </c>
+      <c r="B390" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A391" t="s">
+        <v>742</v>
+      </c>
+      <c r="B391" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A392" t="s">
+        <v>743</v>
+      </c>
+      <c r="B392" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A393" t="s">
+        <v>744</v>
+      </c>
+      <c r="B393" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A394" t="s">
+        <v>745</v>
+      </c>
+      <c r="B394" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A395" t="s">
+        <v>746</v>
+      </c>
+      <c r="B395" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A396" t="s">
+        <v>747</v>
+      </c>
+      <c r="B396" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A397" t="s">
+        <v>748</v>
+      </c>
+      <c r="B397" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A398" t="s">
+        <v>749</v>
+      </c>
+      <c r="B398" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A399" t="s">
+        <v>750</v>
+      </c>
+      <c r="B399" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A400" t="s">
+        <v>751</v>
+      </c>
+      <c r="B400" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A401" t="s">
+        <v>752</v>
+      </c>
+      <c r="B401" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A402" t="s">
+        <v>753</v>
+      </c>
+      <c r="B402" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A403" t="s">
+        <v>754</v>
+      </c>
+      <c r="B403" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A404" t="s">
+        <v>755</v>
+      </c>
+      <c r="B404" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A405" t="s">
+        <v>756</v>
+      </c>
+      <c r="B405" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A406" t="s">
+        <v>757</v>
+      </c>
+      <c r="B406" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A407" t="s">
+        <v>758</v>
+      </c>
+      <c r="B407" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A408" t="s">
+        <v>759</v>
+      </c>
+      <c r="B408" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A409" t="s">
+        <v>760</v>
+      </c>
+      <c r="B409" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A410" t="s">
+        <v>761</v>
+      </c>
+      <c r="B410" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A411" t="s">
+        <v>762</v>
+      </c>
+      <c r="B411" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A412" t="s">
+        <v>763</v>
+      </c>
+      <c r="B412" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A413" t="s">
+        <v>764</v>
+      </c>
+      <c r="B413" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A414" t="s">
+        <v>765</v>
+      </c>
+      <c r="B414" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A415" t="s">
+        <v>766</v>
+      </c>
+      <c r="B415" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A416" t="s">
+        <v>767</v>
+      </c>
+      <c r="B416" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A417" t="s">
+        <v>768</v>
+      </c>
+      <c r="B417" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A418" t="s">
+        <v>769</v>
+      </c>
+      <c r="B418" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A419" t="s">
+        <v>770</v>
+      </c>
+      <c r="B419" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A420" t="s">
+        <v>771</v>
+      </c>
+      <c r="B420" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A421" t="s">
+        <v>772</v>
+      </c>
+      <c r="B421" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A422" t="s">
+        <v>773</v>
+      </c>
+      <c r="B422" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A423" t="s">
+        <v>774</v>
+      </c>
+      <c r="B423" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A424" t="s">
+        <v>775</v>
+      </c>
+      <c r="B424" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A425" t="s">
+        <v>776</v>
+      </c>
+      <c r="B425" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A426" t="s">
+        <v>777</v>
+      </c>
+      <c r="B426" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A427" t="s">
+        <v>778</v>
+      </c>
+      <c r="B427" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A428" t="s">
+        <v>779</v>
+      </c>
+      <c r="B428" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A429" t="s">
+        <v>780</v>
+      </c>
+      <c r="B429" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A430" t="s">
+        <v>781</v>
+      </c>
+      <c r="B430" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A431" t="s">
+        <v>782</v>
+      </c>
+      <c r="B431" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A432" t="s">
+        <v>783</v>
+      </c>
+      <c r="B432" t="s">
         <v>23</v>
       </c>
     </row>

--- a/Pyhton Programs.xlsx
+++ b/Pyhton Programs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workplace\Python-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA84DC82-0CA4-4966-BBE1-812E8FB0747D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AAF6C0D-531F-478B-BD2E-717DE9BEA5FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1128" yWindow="1416" windowWidth="18816" windowHeight="11544" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
+    <workbookView xWindow="1128" yWindow="696" windowWidth="18816" windowHeight="11544" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
   </bookViews>
   <sheets>
     <sheet name="Python" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1429" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="806">
   <si>
     <t>Program NO</t>
   </si>
@@ -2614,6 +2614,33 @@
   </si>
   <si>
     <t>1       *       3       *       5       *</t>
+  </si>
+  <si>
+    <t>1       *       2       *       3       *       4       *       5</t>
+  </si>
+  <si>
+    <t>Reverse of number using recursion using global variables</t>
+  </si>
+  <si>
+    <t>Reverse of number using recursion Withot global variable</t>
+  </si>
+  <si>
+    <t>Sorting Dictionary Values</t>
+  </si>
+  <si>
+    <t>a b c d e f g</t>
+  </si>
+  <si>
+    <t>A        *       B       *       C       *       D</t>
+  </si>
+  <si>
+    <t>A        2       B       4       C       6       D</t>
+  </si>
+  <si>
+    <t>A        b       C       d       E       f       G</t>
+  </si>
+  <si>
+    <t>*       *       *       #        #       #       *      *       *       #        #    For input == 1</t>
   </si>
 </sst>
 </file>
@@ -4775,6 +4802,9 @@
       <c r="B159" t="s">
         <v>23</v>
       </c>
+      <c r="C159" t="s">
+        <v>797</v>
+      </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
@@ -4783,64 +4813,88 @@
       <c r="B160" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C160" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>512</v>
       </c>
       <c r="B161" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C161" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>513</v>
       </c>
       <c r="B162" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C162" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>514</v>
       </c>
       <c r="B163" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C163" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>515</v>
       </c>
       <c r="B164" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C164" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>516</v>
       </c>
       <c r="B165" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C165" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>517</v>
       </c>
       <c r="B166" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C166" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>518</v>
       </c>
       <c r="B167" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C167" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>519</v>
       </c>
@@ -4848,7 +4902,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>520</v>
       </c>
@@ -4856,7 +4910,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>521</v>
       </c>
@@ -4864,7 +4918,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>522</v>
       </c>
@@ -4872,7 +4926,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>523</v>
       </c>
@@ -4880,7 +4934,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>524</v>
       </c>
@@ -4888,7 +4942,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>525</v>
       </c>
@@ -4896,7 +4950,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>526</v>
       </c>
@@ -4904,7 +4958,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>527</v>
       </c>

--- a/Pyhton Programs.xlsx
+++ b/Pyhton Programs.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workplace\Python-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AAF6C0D-531F-478B-BD2E-717DE9BEA5FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75D9979F-F5B5-4811-A92C-8A9A2C170A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1128" yWindow="696" windowWidth="18816" windowHeight="11544" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
+    <workbookView xWindow="1128" yWindow="696" windowWidth="18816" windowHeight="11544" activeTab="1" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
   </bookViews>
   <sheets>
     <sheet name="Python" sheetId="1" r:id="rId1"/>
-    <sheet name="JavaScript" sheetId="2" r:id="rId2"/>
+    <sheet name="C++" sheetId="3" r:id="rId2"/>
+    <sheet name="JavaScript" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="841">
   <si>
     <t>Program NO</t>
   </si>
@@ -2641,6 +2642,124 @@
   </si>
   <si>
     <t>*       *       *       #        #       #       *      *       *       #        #    For input == 1</t>
+  </si>
+  <si>
+    <t>Def main function and calling Main()</t>
+  </si>
+  <si>
+    <t>Printing Pyramid</t>
+  </si>
+  <si>
+    <t>Inverted Pyramid Triangle</t>
+  </si>
+  <si>
+    <t>Upper to Lower Pyrmaid</t>
+  </si>
+  <si>
+    <t>One side touched Pyramid</t>
+  </si>
+  <si>
+    <t>Printing ButterFly</t>
+  </si>
+  <si>
+    <t>Left sided touched Right angled Triangle</t>
+  </si>
+  <si>
+    <t>Right sided touched Right angled Triangle</t>
+  </si>
+  <si>
+    <t>Half Butterfly Printing Pattern</t>
+  </si>
+  <si>
+    <t>Printing Jay Ganesh Using def main() : finction</t>
+  </si>
+  <si>
+    <t>Size Of Empty String</t>
+  </si>
+  <si>
+    <t>String UserDefined Functions'</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Creating Own Package of String name from </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Package.StringX import StringX</t>
+    </r>
+  </si>
+  <si>
+    <t>C++</t>
+  </si>
+  <si>
+    <t>Printing Jay Ganesh</t>
+  </si>
+  <si>
+    <t>Printing Address Of Variable</t>
+  </si>
+  <si>
+    <t>program2</t>
+  </si>
+  <si>
+    <t>program3</t>
+  </si>
+  <si>
+    <t>Comparing Values</t>
+  </si>
+  <si>
+    <t>program4</t>
+  </si>
+  <si>
+    <t>program5</t>
+  </si>
+  <si>
+    <t>program6</t>
+  </si>
+  <si>
+    <t>program7</t>
+  </si>
+  <si>
+    <t>program8</t>
+  </si>
+  <si>
+    <t>program9</t>
+  </si>
+  <si>
+    <t>program10</t>
+  </si>
+  <si>
+    <t>program11</t>
+  </si>
+  <si>
+    <t>program12</t>
+  </si>
+  <si>
+    <t>program13</t>
+  </si>
+  <si>
+    <t>program14</t>
+  </si>
+  <si>
+    <t>program15</t>
+  </si>
+  <si>
+    <t>program16</t>
+  </si>
+  <si>
+    <t>program17</t>
+  </si>
+  <si>
+    <t>Boolean Datatype added in C++</t>
+  </si>
+  <si>
+    <t>Greatest Of Three Number in C++</t>
   </si>
 </sst>
 </file>
@@ -5094,7 +5213,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>544</v>
       </c>
@@ -5102,7 +5221,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>545</v>
       </c>
@@ -5110,7 +5229,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>546</v>
       </c>
@@ -5118,7 +5237,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>547</v>
       </c>
@@ -5126,7 +5245,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>548</v>
       </c>
@@ -5134,55 +5253,73 @@
         <v>23</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>549</v>
       </c>
       <c r="B198" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C198" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>550</v>
       </c>
       <c r="B199" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C199" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>551</v>
       </c>
       <c r="B200" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C200" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>552</v>
       </c>
       <c r="B201" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C201" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>553</v>
       </c>
       <c r="B202" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C202" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>554</v>
       </c>
       <c r="B203" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C203" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>555</v>
       </c>
@@ -5190,63 +5327,84 @@
         <v>23</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>556</v>
       </c>
       <c r="B205" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C205" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>557</v>
       </c>
       <c r="B206" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C206" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>558</v>
       </c>
       <c r="B207" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C207" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>559</v>
       </c>
       <c r="B208" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C208" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>560</v>
       </c>
       <c r="B209" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C209" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>561</v>
       </c>
       <c r="B210" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C210" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>562</v>
       </c>
       <c r="B211" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C211" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>563</v>
       </c>
@@ -5254,7 +5412,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>564</v>
       </c>
@@ -5262,7 +5420,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>565</v>
       </c>
@@ -5270,7 +5428,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>566</v>
       </c>
@@ -5278,7 +5436,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>567</v>
       </c>
@@ -5286,7 +5444,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>568</v>
       </c>
@@ -5294,7 +5452,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>569</v>
       </c>
@@ -5302,7 +5460,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>570</v>
       </c>
@@ -5310,7 +5468,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>571</v>
       </c>
@@ -5318,7 +5476,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>572</v>
       </c>
@@ -5326,7 +5484,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>573</v>
       </c>
@@ -5334,7 +5492,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>574</v>
       </c>
@@ -5342,7 +5500,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>575</v>
       </c>
@@ -7022,6 +7180,219 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C54D698-06A1-48AE-8A3C-6305D184DEC5}">
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>819</v>
+      </c>
+      <c r="C2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>822</v>
+      </c>
+      <c r="B3" t="s">
+        <v>819</v>
+      </c>
+      <c r="C3" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>823</v>
+      </c>
+      <c r="B4" t="s">
+        <v>819</v>
+      </c>
+      <c r="C4" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>825</v>
+      </c>
+      <c r="B5" t="s">
+        <v>819</v>
+      </c>
+      <c r="C5" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>826</v>
+      </c>
+      <c r="B6" t="s">
+        <v>819</v>
+      </c>
+      <c r="C6" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>827</v>
+      </c>
+      <c r="B7" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>828</v>
+      </c>
+      <c r="B8" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>829</v>
+      </c>
+      <c r="B9" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>830</v>
+      </c>
+      <c r="B10" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>831</v>
+      </c>
+      <c r="B11" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>832</v>
+      </c>
+      <c r="B12" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>833</v>
+      </c>
+      <c r="B13" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>834</v>
+      </c>
+      <c r="B14" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>835</v>
+      </c>
+      <c r="B15" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>836</v>
+      </c>
+      <c r="B16" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>837</v>
+      </c>
+      <c r="B17" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>838</v>
+      </c>
+      <c r="B18" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>819</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43850411-BEF7-434C-A82A-CCD83C8B451E}">
   <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/Pyhton Programs.xlsx
+++ b/Pyhton Programs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workplace\Python-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75D9979F-F5B5-4811-A92C-8A9A2C170A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0849893-3B09-4F48-8F29-0417388F3305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1128" yWindow="696" windowWidth="18816" windowHeight="11544" activeTab="1" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
+    <workbookView xWindow="1128" yWindow="696" windowWidth="18816" windowHeight="11544" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
   </bookViews>
   <sheets>
     <sheet name="Python" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="841">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="878">
   <si>
     <t>Program NO</t>
   </si>
@@ -2760,6 +2760,140 @@
   </si>
   <si>
     <t>Greatest Of Three Number in C++</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Printing </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>decimal,octal and hexadecimal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in number in python</t>
+    </r>
+  </si>
+  <si>
+    <t>Priting binary of number but in reverse order</t>
+  </si>
+  <si>
+    <t>Result of and(&amp;) operator</t>
+  </si>
+  <si>
+    <t>Result of Or(|) operator</t>
+  </si>
+  <si>
+    <t>Result pf XOR(^) operator</t>
+  </si>
+  <si>
+    <t>Combine result of all operation</t>
+  </si>
+  <si>
+    <t>Counting number of 1's in Binary Number System</t>
+  </si>
+  <si>
+    <t>Modification of previous code</t>
+  </si>
+  <si>
+    <t>Finding Paerticular bit is On OR OFF</t>
+  </si>
+  <si>
+    <t>checking 7 th bit is On or OFF</t>
+  </si>
+  <si>
+    <t>Checking 13th bit is on or off</t>
+  </si>
+  <si>
+    <t>checking 17th bit is on or off</t>
+  </si>
+  <si>
+    <t>checking 17th bit is on or off using hexadecimal number</t>
+  </si>
+  <si>
+    <t>Checking 13th bit is on or off using hexadeciaml number</t>
+  </si>
+  <si>
+    <t>Enter particular bit to find out bit is on or off</t>
+  </si>
+  <si>
+    <t>Priting Deciaml number in bit but by using left shift operator</t>
+  </si>
+  <si>
+    <t>Printin Hexadecimal number bit by in hexadeciaml foramt</t>
+  </si>
+  <si>
+    <t>Printing 1 to 100 devimal number and hexadeciam number</t>
+  </si>
+  <si>
+    <t>Printing 1 to 1000 devimal number and hexadeciam number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">printing bits and number of deciaml number that we can write </t>
+  </si>
+  <si>
+    <t>printing bits and number of deciaml number that we can write (HEXADECIAML)</t>
+  </si>
+  <si>
+    <t>Getting oner more bit 33</t>
+  </si>
+  <si>
+    <t>Prtinting in reverse orede bits and limit of deciaml number it can store</t>
+  </si>
+  <si>
+    <t>Overflow the bits</t>
+  </si>
+  <si>
+    <t>Smallest value of int</t>
+  </si>
+  <si>
+    <t>Largest value of int</t>
+  </si>
+  <si>
+    <t>used To Toggle the particular bit BIT NUMBER 4</t>
+  </si>
+  <si>
+    <t>used To Toggle the particular bit BIT NUMBER 11</t>
+  </si>
+  <si>
+    <t>Code For toggle particular bit</t>
+  </si>
+  <si>
+    <t>Creating Toggle function</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Updating the Ipos condition </t>
+  </si>
+  <si>
+    <t>OffBbit Function</t>
+  </si>
+  <si>
+    <t>making 4th bit off of number</t>
+  </si>
+  <si>
+    <t>making 13th bit off of number</t>
+  </si>
+  <si>
+    <t>OffBbit Function at particular bit positon</t>
+  </si>
+  <si>
+    <t>Neagation of laggest deciamal number</t>
+  </si>
+  <si>
+    <t>changing value of two bit position</t>
   </si>
 </sst>
 </file>
@@ -5411,6 +5545,9 @@
       <c r="B212" t="s">
         <v>23</v>
       </c>
+      <c r="C212" t="s">
+        <v>841</v>
+      </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
@@ -5419,6 +5556,9 @@
       <c r="B213" t="s">
         <v>23</v>
       </c>
+      <c r="C213" t="s">
+        <v>842</v>
+      </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
@@ -5427,6 +5567,9 @@
       <c r="B214" t="s">
         <v>23</v>
       </c>
+      <c r="C214" t="s">
+        <v>843</v>
+      </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
@@ -5435,6 +5578,9 @@
       <c r="B215" t="s">
         <v>23</v>
       </c>
+      <c r="C215" t="s">
+        <v>844</v>
+      </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
@@ -5443,6 +5589,9 @@
       <c r="B216" t="s">
         <v>23</v>
       </c>
+      <c r="C216" t="s">
+        <v>845</v>
+      </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
@@ -5451,6 +5600,9 @@
       <c r="B217" t="s">
         <v>23</v>
       </c>
+      <c r="C217" t="s">
+        <v>846</v>
+      </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
@@ -5459,6 +5611,9 @@
       <c r="B218" t="s">
         <v>23</v>
       </c>
+      <c r="C218" t="s">
+        <v>847</v>
+      </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
@@ -5467,6 +5622,9 @@
       <c r="B219" t="s">
         <v>23</v>
       </c>
+      <c r="C219" t="s">
+        <v>848</v>
+      </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
@@ -5475,6 +5633,9 @@
       <c r="B220" t="s">
         <v>23</v>
       </c>
+      <c r="C220" t="s">
+        <v>849</v>
+      </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
@@ -5483,6 +5644,9 @@
       <c r="B221" t="s">
         <v>23</v>
       </c>
+      <c r="C221" t="s">
+        <v>850</v>
+      </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
@@ -5491,6 +5655,9 @@
       <c r="B222" t="s">
         <v>23</v>
       </c>
+      <c r="C222" t="s">
+        <v>851</v>
+      </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
@@ -5499,6 +5666,9 @@
       <c r="B223" t="s">
         <v>23</v>
       </c>
+      <c r="C223" t="s">
+        <v>852</v>
+      </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
@@ -5507,192 +5677,264 @@
       <c r="B224" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C224" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>576</v>
       </c>
       <c r="B225" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C225" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>577</v>
       </c>
       <c r="B226" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C226" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>578</v>
       </c>
       <c r="B227" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C227" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>579</v>
       </c>
       <c r="B228" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C228" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>580</v>
       </c>
       <c r="B229" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C229" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>581</v>
       </c>
       <c r="B230" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C230" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>582</v>
       </c>
       <c r="B231" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C231" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>583</v>
       </c>
       <c r="B232" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C232" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>584</v>
       </c>
       <c r="B233" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C233" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>585</v>
       </c>
       <c r="B234" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C234" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>586</v>
       </c>
       <c r="B235" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C235" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>587</v>
       </c>
       <c r="B236" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C236" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>588</v>
       </c>
       <c r="B237" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C237" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>589</v>
       </c>
       <c r="B238" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C238" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>590</v>
       </c>
       <c r="B239" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C239" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>591</v>
       </c>
       <c r="B240" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C240" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>592</v>
       </c>
       <c r="B241" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C241" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>593</v>
       </c>
       <c r="B242" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C242" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>594</v>
       </c>
       <c r="B243" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C243" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>595</v>
       </c>
       <c r="B244" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C244" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>596</v>
       </c>
       <c r="B245" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C245" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>597</v>
       </c>
       <c r="B246" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C246" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>598</v>
       </c>
       <c r="B247" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C247" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>599</v>
       </c>
@@ -5700,15 +5942,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>600</v>
       </c>
       <c r="B249" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C249" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>601</v>
       </c>
@@ -5716,7 +5961,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>602</v>
       </c>
@@ -5724,7 +5969,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>603</v>
       </c>
@@ -5732,7 +5977,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>604</v>
       </c>
@@ -5740,7 +5985,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>605</v>
       </c>
@@ -5748,7 +5993,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>606</v>
       </c>
@@ -5756,7 +6001,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>607</v>
       </c>

--- a/Pyhton Programs.xlsx
+++ b/Pyhton Programs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workplace\GIIT_HUB_CODES\Python-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5B4899-8FF3-4798-90DD-6E305F345716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665E2C2A-6A60-4F9B-8E82-D44FA248D0BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2220" yWindow="768" windowWidth="18816" windowHeight="11544" activeTab="1" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
+    <workbookView xWindow="2220" yWindow="696" windowWidth="18816" windowHeight="11544" activeTab="1" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
   </bookViews>
   <sheets>
     <sheet name="Python" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3590" uniqueCount="1785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3648" uniqueCount="1842">
   <si>
     <t>Program NO</t>
   </si>
@@ -5696,6 +5696,249 @@
   </si>
   <si>
     <t>Exception Handling in C++</t>
+  </si>
+  <si>
+    <t>Creating structure of linkelist named node</t>
+  </si>
+  <si>
+    <t>Created node and connect them to each other</t>
+  </si>
+  <si>
+    <t>Adding loop to previous code</t>
+  </si>
+  <si>
+    <t>Printing address of Node present in Linkelidt</t>
+  </si>
+  <si>
+    <t>Adding Display function extra to class</t>
+  </si>
+  <si>
+    <t>Adding count method function to class</t>
+  </si>
+  <si>
+    <t>creating another class named linkdlist and create new function InsertFirst</t>
+  </si>
+  <si>
+    <t>InsertLast function is added</t>
+  </si>
+  <si>
+    <t>DeleteFirst function is added</t>
+  </si>
+  <si>
+    <t>DeleteLast function is added</t>
+  </si>
+  <si>
+    <t>InsertAtPos and DeleteAtPos function is added</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Throw userdefined exception </t>
+  </si>
+  <si>
+    <t>casting upcastin , downcasting, and No casting samll capacity of data poinitng to large capacity of data that is upcasting</t>
+  </si>
+  <si>
+    <t>OOP Overrinidng in CPP understanding how vitural function works and how vtable comes and how vptr comes</t>
+  </si>
+  <si>
+    <t>OOP Pure Virtutal function in  CPP and understanding of concrete nad abstract function derived class should provide the function body itherwise error comes</t>
+  </si>
+  <si>
+    <t>pure virtual function</t>
+  </si>
+  <si>
+    <t>String IN CPP char Arr[6],char Arr[],char *Arr,char Arr[]</t>
+  </si>
+  <si>
+    <t>Namespace in cpp</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Input of whole string buusing </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getline(cin,String_name)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Input of character array of string using </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cin.getline(Arr,20) cin.getlinr(Array_name,size_ofArr)</t>
+    </r>
+  </si>
+  <si>
+    <t>Creating own namespace which Getting Character array as input until new characters enter</t>
+  </si>
+  <si>
+    <t>Creating own StrlneX function Count the length of string</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creating own StrCpy Function </t>
+  </si>
+  <si>
+    <t>Creatin StrCatX function which return concatenated String</t>
+  </si>
+  <si>
+    <t>Crating string Compare function</t>
+  </si>
+  <si>
+    <t>Creating String Function which will conifirm character present or not</t>
+  </si>
+  <si>
+    <t>Adding function that will return true if string is present in parent string else return false</t>
+  </si>
+  <si>
+    <t>Adding StrRev Function</t>
+  </si>
+  <si>
+    <t>Getline Built in function for taking input through until next line enters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">derived datatype String and understanding some built in function </t>
+  </si>
+  <si>
+    <t>Pattern Printing In CPP</t>
+  </si>
+  <si>
+    <t>GCD Of two numbers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">display digit of a number </t>
+  </si>
+  <si>
+    <t>Sum of a digit of a number</t>
+  </si>
+  <si>
+    <t>Reverse of a Number</t>
+  </si>
+  <si>
+    <t>Count freuency of a particular digit in a number</t>
+  </si>
+  <si>
+    <t>Check Number Is palindrome or not</t>
+  </si>
+  <si>
+    <t>Creating Array of Object the it will multiple time its constructor</t>
+  </si>
+  <si>
+    <t>Checking some fact of object array</t>
+  </si>
+  <si>
+    <t>Display the array function</t>
+  </si>
+  <si>
+    <t>Summation of array function</t>
+  </si>
+  <si>
+    <t>Printing Even Number in array</t>
+  </si>
+  <si>
+    <t>Printing Odd Number In array</t>
+  </si>
+  <si>
+    <t>Linearsearch In array</t>
+  </si>
+  <si>
+    <t>Friend concept in C++ (friend concept only is in CPP)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">we can define in class as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>friend void fun();</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> that means fun() is now access all type of membes in class</t>
+    </r>
+  </si>
+  <si>
+    <t>the function which can not friend can not access the class members</t>
+  </si>
+  <si>
+    <r>
+      <t>the function which will be a part of calss will be friend of a class by defining in that class</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> friend void Hello :: fun(); </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>then the fun() function in Hello become only friend of that class</t>
+    </r>
+  </si>
+  <si>
+    <t>but there is problem in above code because of compiled language there is one problem that compiler Will find the class but unable to find to resolve these we first declare the function declare at start</t>
+  </si>
+  <si>
+    <t>the clear code and runnable code of friend concept</t>
+  </si>
+  <si>
+    <t>Specific code in CPP</t>
+  </si>
+  <si>
+    <t>Specific code in class CPP</t>
+  </si>
+  <si>
+    <t>Specific class with multiple function and different prototype</t>
+  </si>
+  <si>
+    <t>Creating Genric function template&lt;class T&gt;</t>
+  </si>
+  <si>
+    <t>There is some problem come when we use template for class</t>
+  </si>
+  <si>
+    <t>for class while declaring object we have to tell as Arithematic  &lt;int&gt;aobj(12,12)</t>
+  </si>
+  <si>
+    <t>for particular template is only used for that particular calss or paricular function</t>
   </si>
 </sst>
 </file>
@@ -8762,6 +9005,9 @@
       <c r="B250" t="s">
         <v>23</v>
       </c>
+      <c r="C250" t="s">
+        <v>1785</v>
+      </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
@@ -8770,6 +9016,9 @@
       <c r="B251" t="s">
         <v>23</v>
       </c>
+      <c r="C251" t="s">
+        <v>1786</v>
+      </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
@@ -8778,6 +9027,9 @@
       <c r="B252" t="s">
         <v>23</v>
       </c>
+      <c r="C252" t="s">
+        <v>1787</v>
+      </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
@@ -8786,6 +9038,9 @@
       <c r="B253" t="s">
         <v>23</v>
       </c>
+      <c r="C253" t="s">
+        <v>1788</v>
+      </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
@@ -8794,6 +9049,9 @@
       <c r="B254" t="s">
         <v>23</v>
       </c>
+      <c r="C254" t="s">
+        <v>1789</v>
+      </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
@@ -8802,6 +9060,9 @@
       <c r="B255" t="s">
         <v>23</v>
       </c>
+      <c r="C255" t="s">
+        <v>1790</v>
+      </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
@@ -8810,40 +9071,55 @@
       <c r="B256" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C256" t="s">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>608</v>
       </c>
       <c r="B257" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C257" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>609</v>
       </c>
       <c r="B258" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C258" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>610</v>
       </c>
       <c r="B259" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C259" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>611</v>
       </c>
       <c r="B260" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C260" t="s">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>612</v>
       </c>
@@ -8851,7 +9127,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>613</v>
       </c>
@@ -8859,7 +9135,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>614</v>
       </c>
@@ -8867,7 +9143,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>615</v>
       </c>
@@ -8875,7 +9151,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>616</v>
       </c>
@@ -8883,7 +9159,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>617</v>
       </c>
@@ -8891,7 +9167,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>618</v>
       </c>
@@ -8899,7 +9175,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>619</v>
       </c>
@@ -8907,7 +9183,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>620</v>
       </c>
@@ -8915,7 +9191,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>621</v>
       </c>
@@ -8923,7 +9199,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>622</v>
       </c>
@@ -8931,7 +9207,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>623</v>
       </c>
@@ -11255,6 +11531,9 @@
       <c r="B93" t="s">
         <v>819</v>
       </c>
+      <c r="C93" t="s">
+        <v>1796</v>
+      </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
@@ -11263,6 +11542,9 @@
       <c r="B94" t="s">
         <v>819</v>
       </c>
+      <c r="C94" t="s">
+        <v>1797</v>
+      </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
@@ -11271,6 +11553,9 @@
       <c r="B95" t="s">
         <v>819</v>
       </c>
+      <c r="C95" t="s">
+        <v>1798</v>
+      </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
@@ -11279,144 +11564,198 @@
       <c r="B96" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C96" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>967</v>
       </c>
       <c r="B97" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C97" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>968</v>
       </c>
       <c r="B98" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C98" t="s">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>969</v>
       </c>
       <c r="B99" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C99" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>970</v>
       </c>
       <c r="B100" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C100" t="s">
+        <v>1803</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>971</v>
       </c>
       <c r="B101" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C101" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>972</v>
       </c>
       <c r="B102" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C102" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>973</v>
       </c>
       <c r="B103" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C103" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>974</v>
       </c>
       <c r="B104" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C104" t="s">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>975</v>
       </c>
       <c r="B105" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C105" t="s">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>976</v>
       </c>
       <c r="B106" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C106" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>977</v>
       </c>
       <c r="B107" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C107" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>978</v>
       </c>
       <c r="B108" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C108" t="s">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>979</v>
       </c>
       <c r="B109" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C109" t="s">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>980</v>
       </c>
       <c r="B110" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C110" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>981</v>
       </c>
       <c r="B111" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C111" t="s">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>982</v>
       </c>
       <c r="B112" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C112" t="s">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>983</v>
       </c>
       <c r="B113" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C113" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>984</v>
       </c>
@@ -11424,7 +11763,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>985</v>
       </c>
@@ -11432,7 +11771,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>986</v>
       </c>
@@ -11440,7 +11779,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>987</v>
       </c>
@@ -11448,7 +11787,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>988</v>
       </c>
@@ -11456,7 +11795,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>989</v>
       </c>
@@ -11464,7 +11803,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>990</v>
       </c>
@@ -11472,7 +11811,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>991</v>
       </c>
@@ -11480,7 +11819,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>992</v>
       </c>
@@ -11488,7 +11827,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>993</v>
       </c>
@@ -11496,7 +11835,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>994</v>
       </c>
@@ -11504,7 +11843,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>995</v>
       </c>
@@ -11512,7 +11851,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>996</v>
       </c>
@@ -11520,7 +11859,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>997</v>
       </c>
@@ -11528,7 +11867,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>998</v>
       </c>
@@ -11792,7 +12131,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>1031</v>
       </c>
@@ -11800,7 +12139,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>1032</v>
       </c>
@@ -11808,7 +12147,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>1033</v>
       </c>
@@ -11816,7 +12155,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>1034</v>
       </c>
@@ -11824,7 +12163,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>1035</v>
       </c>
@@ -11832,7 +12171,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>1036</v>
       </c>
@@ -11840,212 +12179,290 @@
         <v>819</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>1037</v>
       </c>
       <c r="B167" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C167" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>1038</v>
       </c>
       <c r="B168" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C168" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>1039</v>
       </c>
       <c r="B169" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C169" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>1040</v>
       </c>
       <c r="B170" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C170" t="s">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>1041</v>
       </c>
       <c r="B171" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C171" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>1042</v>
       </c>
       <c r="B172" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C172" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>1043</v>
       </c>
       <c r="B173" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C173" t="s">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>1044</v>
       </c>
       <c r="B174" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C174" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>1045</v>
       </c>
       <c r="B175" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C175" t="s">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>1046</v>
       </c>
       <c r="B176" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C176" t="s">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>1047</v>
       </c>
       <c r="B177" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C177" t="s">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>1048</v>
       </c>
       <c r="B178" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C178" t="s">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>1049</v>
       </c>
       <c r="B179" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C179" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>1050</v>
       </c>
       <c r="B180" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C180" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>1051</v>
       </c>
       <c r="B181" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C181" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>1052</v>
       </c>
       <c r="B182" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C182" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>1053</v>
       </c>
       <c r="B183" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C183" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>1054</v>
       </c>
       <c r="B184" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C184" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>1055</v>
       </c>
       <c r="B185" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C185" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>1056</v>
       </c>
       <c r="B186" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C186" t="s">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>1057</v>
       </c>
       <c r="B187" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C187" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>1058</v>
       </c>
       <c r="B188" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C188" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>1059</v>
       </c>
       <c r="B189" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C189" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>1060</v>
       </c>
       <c r="B190" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C190" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>1061</v>
       </c>
       <c r="B191" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C191" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>1062</v>
       </c>
       <c r="B192" t="s">
         <v>819</v>
+      </c>
+      <c r="C192" t="s">
+        <v>1841</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">

--- a/Pyhton Programs.xlsx
+++ b/Pyhton Programs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workplace\GIIT_HUB_CODES\Python-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665E2C2A-6A60-4F9B-8E82-D44FA248D0BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D56F0DA1-EF98-47CA-9EA0-B0AE2F32D8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2220" yWindow="696" windowWidth="18816" windowHeight="11544" activeTab="1" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
+    <workbookView xWindow="2220" yWindow="696" windowWidth="18816" windowHeight="11544" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
   </bookViews>
   <sheets>
     <sheet name="Python" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3648" uniqueCount="1842">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3649" uniqueCount="1843">
   <si>
     <t>Program NO</t>
   </si>
@@ -5939,6 +5939,9 @@
   </si>
   <si>
     <t>for particular template is only used for that particular calss or paricular function</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adding search function </t>
   </si>
 </sst>
 </file>
@@ -9126,6 +9129,9 @@
       <c r="B261" t="s">
         <v>23</v>
       </c>
+      <c r="C261" t="s">
+        <v>1842</v>
+      </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">

--- a/Pyhton Programs.xlsx
+++ b/Pyhton Programs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workplace\GIIT_HUB_CODES\Python-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D56F0DA1-EF98-47CA-9EA0-B0AE2F32D8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D511834-5FD4-499D-9A13-8BC97CED8836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2220" yWindow="696" windowWidth="18816" windowHeight="11544" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3649" uniqueCount="1843">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3664" uniqueCount="1858">
   <si>
     <t>Program NO</t>
   </si>
@@ -5942,6 +5942,51 @@
   </si>
   <si>
     <t xml:space="preserve">Adding search function </t>
+  </si>
+  <si>
+    <t>Count Even Function of Singly linkedlist</t>
+  </si>
+  <si>
+    <t>Count Odd Node in Singly Linkedlist</t>
+  </si>
+  <si>
+    <t>Frequency of Particular node function in SinglyLinkedlist</t>
+  </si>
+  <si>
+    <t>DisplayEven() to display on even node of Linkedlist</t>
+  </si>
+  <si>
+    <t>DisplayFirstOccur() function</t>
+  </si>
+  <si>
+    <t>DisplayLastOccur() function in Singly Linear Linkedlist</t>
+  </si>
+  <si>
+    <t>Craeting DoublyLinearLinkedlist</t>
+  </si>
+  <si>
+    <t>InsertFirst() Function of Doubly Linear Linkedlist</t>
+  </si>
+  <si>
+    <t>Adding Count and Display Function Doubly Linkedlist</t>
+  </si>
+  <si>
+    <t>InsertLast() function of Doubly Linear Linkedlist</t>
+  </si>
+  <si>
+    <t>DeleteFirst() Function in Doubly Linear Linkedlist</t>
+  </si>
+  <si>
+    <t>DeleteLAst() Function in Doubly Linear Linkedlist</t>
+  </si>
+  <si>
+    <t>InsertAtPos() function in Doubly Linear linkedList</t>
+  </si>
+  <si>
+    <t>DeleteAtPos() function IN Doubly Linear Linkedlist</t>
+  </si>
+  <si>
+    <t>Singly Circular Linkedlist All function()</t>
   </si>
 </sst>
 </file>
@@ -9140,6 +9185,9 @@
       <c r="B262" t="s">
         <v>23</v>
       </c>
+      <c r="C262" t="s">
+        <v>1843</v>
+      </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
@@ -9148,6 +9196,9 @@
       <c r="B263" t="s">
         <v>23</v>
       </c>
+      <c r="C263" t="s">
+        <v>1844</v>
+      </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
@@ -9156,6 +9207,9 @@
       <c r="B264" t="s">
         <v>23</v>
       </c>
+      <c r="C264" t="s">
+        <v>1845</v>
+      </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
@@ -9164,6 +9218,9 @@
       <c r="B265" t="s">
         <v>23</v>
       </c>
+      <c r="C265" t="s">
+        <v>1846</v>
+      </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
@@ -9172,6 +9229,9 @@
       <c r="B266" t="s">
         <v>23</v>
       </c>
+      <c r="C266" t="s">
+        <v>1847</v>
+      </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
@@ -9180,6 +9240,9 @@
       <c r="B267" t="s">
         <v>23</v>
       </c>
+      <c r="C267" t="s">
+        <v>1848</v>
+      </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
@@ -9188,6 +9251,9 @@
       <c r="B268" t="s">
         <v>23</v>
       </c>
+      <c r="C268" t="s">
+        <v>1849</v>
+      </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
@@ -9196,6 +9262,9 @@
       <c r="B269" t="s">
         <v>23</v>
       </c>
+      <c r="C269" t="s">
+        <v>1850</v>
+      </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
@@ -9204,6 +9273,9 @@
       <c r="B270" t="s">
         <v>23</v>
       </c>
+      <c r="C270" t="s">
+        <v>1851</v>
+      </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
@@ -9212,6 +9284,9 @@
       <c r="B271" t="s">
         <v>23</v>
       </c>
+      <c r="C271" t="s">
+        <v>1852</v>
+      </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
@@ -9220,40 +9295,55 @@
       <c r="B272" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C272" t="s">
+        <v>1853</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>624</v>
       </c>
       <c r="B273" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C273" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>625</v>
       </c>
       <c r="B274" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C274" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>626</v>
       </c>
       <c r="B275" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C275" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>627</v>
       </c>
       <c r="B276" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C276" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>628</v>
       </c>
@@ -9261,7 +9351,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>629</v>
       </c>
@@ -9269,7 +9359,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>630</v>
       </c>
@@ -9277,7 +9367,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>631</v>
       </c>
@@ -9285,7 +9375,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>632</v>
       </c>
@@ -9293,7 +9383,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>633</v>
       </c>
@@ -9301,7 +9391,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>634</v>
       </c>
@@ -9309,7 +9399,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>635</v>
       </c>
@@ -9317,7 +9407,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>636</v>
       </c>
@@ -9325,7 +9415,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>637</v>
       </c>
@@ -9333,7 +9423,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>638</v>
       </c>
@@ -9341,7 +9431,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>639</v>
       </c>

--- a/Pyhton Programs.xlsx
+++ b/Pyhton Programs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workplace\GIIT_HUB_CODES\Python-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D511834-5FD4-499D-9A13-8BC97CED8836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE58DBD8-7877-4EFB-901F-71CE0CD49DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2220" yWindow="696" windowWidth="18816" windowHeight="11544" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
+    <workbookView xWindow="2220" yWindow="696" windowWidth="18816" windowHeight="11544" activeTab="2" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
   </bookViews>
   <sheets>
     <sheet name="Python" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3664" uniqueCount="1858">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3676" uniqueCount="1870">
   <si>
     <t>Program NO</t>
   </si>
@@ -5586,9 +5586,6 @@
     <t>OOP creating parametrized constructor to initialise characterstics</t>
   </si>
   <si>
-    <t>Destructor in java OOP Showing warning</t>
-  </si>
-  <si>
     <t>OOP creating class</t>
   </si>
   <si>
@@ -5987,6 +5984,45 @@
   </si>
   <si>
     <t>Singly Circular Linkedlist All function()</t>
+  </si>
+  <si>
+    <t>Patern Printing using Recursion</t>
+  </si>
+  <si>
+    <t>Pattern Printing IN CPP using Recursion Printing Matrix Of numbre of rows and column</t>
+  </si>
+  <si>
+    <t>Destructor in java OOP Showing warning firstr making refrence null and then call system,gc() it will call destrucor</t>
+  </si>
+  <si>
+    <t>Crating Parametrised constructor</t>
+  </si>
+  <si>
+    <t>this refrence in java is same as this pointer in c++</t>
+  </si>
+  <si>
+    <t>Access specifier in java private can not be accessed by class</t>
+  </si>
+  <si>
+    <t>remove error from from the previous file</t>
+  </si>
+  <si>
+    <t>Input  outut in java using scanner class Scanner sobj = new Scanner();</t>
+  </si>
+  <si>
+    <t>static in java and how to in tialise the static bloack</t>
+  </si>
+  <si>
+    <t>inheritance in java single level</t>
+  </si>
+  <si>
+    <t>multilevel level Inheritnace in java</t>
+  </si>
+  <si>
+    <t>multiple level inheritance is not provided by java</t>
+  </si>
+  <si>
+    <t>the object able to only call those method which are visible to that object</t>
   </si>
 </sst>
 </file>
@@ -9054,7 +9090,7 @@
         <v>23</v>
       </c>
       <c r="C250" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
@@ -9065,7 +9101,7 @@
         <v>23</v>
       </c>
       <c r="C251" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
@@ -9076,7 +9112,7 @@
         <v>23</v>
       </c>
       <c r="C252" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
@@ -9087,7 +9123,7 @@
         <v>23</v>
       </c>
       <c r="C253" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
@@ -9098,7 +9134,7 @@
         <v>23</v>
       </c>
       <c r="C254" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
@@ -9109,7 +9145,7 @@
         <v>23</v>
       </c>
       <c r="C255" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
@@ -9120,7 +9156,7 @@
         <v>23</v>
       </c>
       <c r="C256" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
@@ -9131,7 +9167,7 @@
         <v>23</v>
       </c>
       <c r="C257" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
@@ -9142,7 +9178,7 @@
         <v>23</v>
       </c>
       <c r="C258" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
@@ -9153,7 +9189,7 @@
         <v>23</v>
       </c>
       <c r="C259" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
@@ -9164,7 +9200,7 @@
         <v>23</v>
       </c>
       <c r="C260" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
@@ -9175,7 +9211,7 @@
         <v>23</v>
       </c>
       <c r="C261" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
@@ -9186,7 +9222,7 @@
         <v>23</v>
       </c>
       <c r="C262" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
@@ -9197,7 +9233,7 @@
         <v>23</v>
       </c>
       <c r="C263" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
@@ -9208,7 +9244,7 @@
         <v>23</v>
       </c>
       <c r="C264" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
@@ -9219,7 +9255,7 @@
         <v>23</v>
       </c>
       <c r="C265" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
@@ -9230,7 +9266,7 @@
         <v>23</v>
       </c>
       <c r="C266" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
@@ -9241,7 +9277,7 @@
         <v>23</v>
       </c>
       <c r="C267" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
@@ -9252,7 +9288,7 @@
         <v>23</v>
       </c>
       <c r="C268" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
@@ -9263,7 +9299,7 @@
         <v>23</v>
       </c>
       <c r="C269" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
@@ -9274,7 +9310,7 @@
         <v>23</v>
       </c>
       <c r="C270" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
@@ -9285,7 +9321,7 @@
         <v>23</v>
       </c>
       <c r="C271" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
@@ -9296,7 +9332,7 @@
         <v>23</v>
       </c>
       <c r="C272" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
@@ -9307,7 +9343,7 @@
         <v>23</v>
       </c>
       <c r="C273" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
@@ -9318,7 +9354,7 @@
         <v>23</v>
       </c>
       <c r="C274" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
@@ -9329,7 +9365,7 @@
         <v>23</v>
       </c>
       <c r="C275" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
@@ -9340,7 +9376,7 @@
         <v>23</v>
       </c>
       <c r="C276" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
@@ -11353,7 +11389,7 @@
         <v>819</v>
       </c>
       <c r="C68" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
@@ -11364,7 +11400,7 @@
         <v>819</v>
       </c>
       <c r="C69" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -11375,7 +11411,7 @@
         <v>819</v>
       </c>
       <c r="C70" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
@@ -11386,7 +11422,7 @@
         <v>819</v>
       </c>
       <c r="C71" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
@@ -11397,7 +11433,7 @@
         <v>819</v>
       </c>
       <c r="C72" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
@@ -11408,7 +11444,7 @@
         <v>819</v>
       </c>
       <c r="C73" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
@@ -11419,7 +11455,7 @@
         <v>819</v>
       </c>
       <c r="C74" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
@@ -11430,7 +11466,7 @@
         <v>819</v>
       </c>
       <c r="C75" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
@@ -11441,7 +11477,7 @@
         <v>819</v>
       </c>
       <c r="C76" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
@@ -11452,7 +11488,7 @@
         <v>819</v>
       </c>
       <c r="C77" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
@@ -11463,7 +11499,7 @@
         <v>819</v>
       </c>
       <c r="C78" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
@@ -11474,7 +11510,7 @@
         <v>819</v>
       </c>
       <c r="C79" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
@@ -11485,7 +11521,7 @@
         <v>819</v>
       </c>
       <c r="C80" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
@@ -11496,7 +11532,7 @@
         <v>819</v>
       </c>
       <c r="C81" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
@@ -11507,7 +11543,7 @@
         <v>819</v>
       </c>
       <c r="C82" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
@@ -11518,7 +11554,7 @@
         <v>819</v>
       </c>
       <c r="C83" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
@@ -11529,7 +11565,7 @@
         <v>819</v>
       </c>
       <c r="C84" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
@@ -11540,7 +11576,7 @@
         <v>819</v>
       </c>
       <c r="C85" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
@@ -11551,7 +11587,7 @@
         <v>819</v>
       </c>
       <c r="C86" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
@@ -11562,7 +11598,7 @@
         <v>819</v>
       </c>
       <c r="C87" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
@@ -11573,7 +11609,7 @@
         <v>819</v>
       </c>
       <c r="C88" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
@@ -11584,7 +11620,7 @@
         <v>819</v>
       </c>
       <c r="C89" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
@@ -11595,7 +11631,7 @@
         <v>819</v>
       </c>
       <c r="C90" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
@@ -11606,7 +11642,7 @@
         <v>819</v>
       </c>
       <c r="C91" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
@@ -11617,7 +11653,7 @@
         <v>819</v>
       </c>
       <c r="C92" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
@@ -11628,7 +11664,7 @@
         <v>819</v>
       </c>
       <c r="C93" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
@@ -11639,7 +11675,7 @@
         <v>819</v>
       </c>
       <c r="C94" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
@@ -11650,7 +11686,7 @@
         <v>819</v>
       </c>
       <c r="C95" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
@@ -11661,7 +11697,7 @@
         <v>819</v>
       </c>
       <c r="C96" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
@@ -11672,7 +11708,7 @@
         <v>819</v>
       </c>
       <c r="C97" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
@@ -11683,7 +11719,7 @@
         <v>819</v>
       </c>
       <c r="C98" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
@@ -11694,7 +11730,7 @@
         <v>819</v>
       </c>
       <c r="C99" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
@@ -11705,7 +11741,7 @@
         <v>819</v>
       </c>
       <c r="C100" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
@@ -11716,7 +11752,7 @@
         <v>819</v>
       </c>
       <c r="C101" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
@@ -11727,7 +11763,7 @@
         <v>819</v>
       </c>
       <c r="C102" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
@@ -11738,7 +11774,7 @@
         <v>819</v>
       </c>
       <c r="C103" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
@@ -11749,7 +11785,7 @@
         <v>819</v>
       </c>
       <c r="C104" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
@@ -11760,7 +11796,7 @@
         <v>819</v>
       </c>
       <c r="C105" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
@@ -11771,7 +11807,7 @@
         <v>819</v>
       </c>
       <c r="C106" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
@@ -11782,7 +11818,7 @@
         <v>819</v>
       </c>
       <c r="C107" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
@@ -11793,7 +11829,7 @@
         <v>819</v>
       </c>
       <c r="C108" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
@@ -11804,7 +11840,7 @@
         <v>819</v>
       </c>
       <c r="C109" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
@@ -11815,7 +11851,7 @@
         <v>819</v>
       </c>
       <c r="C110" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
@@ -11826,7 +11862,7 @@
         <v>819</v>
       </c>
       <c r="C111" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
@@ -11837,7 +11873,7 @@
         <v>819</v>
       </c>
       <c r="C112" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
@@ -11848,7 +11884,7 @@
         <v>819</v>
       </c>
       <c r="C113" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
@@ -12283,7 +12319,7 @@
         <v>819</v>
       </c>
       <c r="C167" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
@@ -12294,7 +12330,7 @@
         <v>819</v>
       </c>
       <c r="C168" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
@@ -12305,7 +12341,7 @@
         <v>819</v>
       </c>
       <c r="C169" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
@@ -12316,7 +12352,7 @@
         <v>819</v>
       </c>
       <c r="C170" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
@@ -12327,7 +12363,7 @@
         <v>819</v>
       </c>
       <c r="C171" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
@@ -12338,7 +12374,7 @@
         <v>819</v>
       </c>
       <c r="C172" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
@@ -12349,7 +12385,7 @@
         <v>819</v>
       </c>
       <c r="C173" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
@@ -12360,7 +12396,7 @@
         <v>819</v>
       </c>
       <c r="C174" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
@@ -12371,7 +12407,7 @@
         <v>819</v>
       </c>
       <c r="C175" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
@@ -12382,7 +12418,7 @@
         <v>819</v>
       </c>
       <c r="C176" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
@@ -12393,7 +12429,7 @@
         <v>819</v>
       </c>
       <c r="C177" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
@@ -12404,7 +12440,7 @@
         <v>819</v>
       </c>
       <c r="C178" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
@@ -12415,7 +12451,7 @@
         <v>819</v>
       </c>
       <c r="C179" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
@@ -12426,7 +12462,7 @@
         <v>819</v>
       </c>
       <c r="C180" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
@@ -12437,7 +12473,7 @@
         <v>819</v>
       </c>
       <c r="C181" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
@@ -12448,7 +12484,7 @@
         <v>819</v>
       </c>
       <c r="C182" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
@@ -12459,7 +12495,7 @@
         <v>819</v>
       </c>
       <c r="C183" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
@@ -12470,7 +12506,7 @@
         <v>819</v>
       </c>
       <c r="C184" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
@@ -12481,7 +12517,7 @@
         <v>819</v>
       </c>
       <c r="C185" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
@@ -12492,7 +12528,7 @@
         <v>819</v>
       </c>
       <c r="C186" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
@@ -12503,7 +12539,7 @@
         <v>819</v>
       </c>
       <c r="C187" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
@@ -12514,7 +12550,7 @@
         <v>819</v>
       </c>
       <c r="C188" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
@@ -12525,7 +12561,7 @@
         <v>819</v>
       </c>
       <c r="C189" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
@@ -12536,7 +12572,7 @@
         <v>819</v>
       </c>
       <c r="C190" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
@@ -12547,7 +12583,7 @@
         <v>819</v>
       </c>
       <c r="C191" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
@@ -12558,10 +12594,10 @@
         <v>819</v>
       </c>
       <c r="C192" t="s">
-        <v>1841</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>1063</v>
       </c>
@@ -12569,7 +12605,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>1064</v>
       </c>
@@ -12577,7 +12613,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>1065</v>
       </c>
@@ -12585,23 +12621,29 @@
         <v>819</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>1066</v>
       </c>
       <c r="B196" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C196" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>1067</v>
       </c>
       <c r="B197" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C197" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>1068</v>
       </c>
@@ -12609,7 +12651,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>1069</v>
       </c>
@@ -12617,7 +12659,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>1070</v>
       </c>
@@ -12625,7 +12667,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>1071</v>
       </c>
@@ -12633,7 +12675,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>1072</v>
       </c>
@@ -12641,7 +12683,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>1073</v>
       </c>
@@ -12649,7 +12691,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>1074</v>
       </c>
@@ -12657,7 +12699,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>1075</v>
       </c>
@@ -12665,7 +12707,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>1076</v>
       </c>
@@ -12673,7 +12715,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>1077</v>
       </c>
@@ -12681,7 +12723,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>1078</v>
       </c>
@@ -15997,7 +16039,7 @@
         <v>1722</v>
       </c>
       <c r="C30" t="s">
-        <v>1759</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -16007,6 +16049,9 @@
       <c r="B31" t="s">
         <v>1722</v>
       </c>
+      <c r="C31" t="s">
+        <v>1860</v>
+      </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
@@ -16015,72 +16060,99 @@
       <c r="B32" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C32" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>72</v>
       </c>
       <c r="B33" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C33" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>73</v>
       </c>
       <c r="B34" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C34" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>74</v>
       </c>
       <c r="B35" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C35" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>75</v>
       </c>
       <c r="B36" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C36" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>76</v>
       </c>
       <c r="B37" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C37" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>77</v>
       </c>
       <c r="B38" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C38" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>78</v>
       </c>
       <c r="B39" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C39" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>79</v>
       </c>
       <c r="B40" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C40" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>80</v>
       </c>
@@ -16088,7 +16160,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>81</v>
       </c>
@@ -16096,7 +16168,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>82</v>
       </c>
@@ -16104,7 +16176,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>83</v>
       </c>
@@ -16112,7 +16184,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>84</v>
       </c>
@@ -16120,7 +16192,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>85</v>
       </c>
@@ -16128,7 +16200,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>86</v>
       </c>
@@ -16136,7 +16208,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>87</v>
       </c>

--- a/Pyhton Programs.xlsx
+++ b/Pyhton Programs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workplace\GIIT_HUB_CODES\Python-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE58DBD8-7877-4EFB-901F-71CE0CD49DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158D1D51-396F-487F-BFAC-872A094F3BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2220" yWindow="696" windowWidth="18816" windowHeight="11544" activeTab="2" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
+    <workbookView xWindow="2220" yWindow="768" windowWidth="18816" windowHeight="11544" activeTab="2" xr2:uid="{934C97BA-48E7-40A5-A4D0-72445425B60C}"/>
   </bookViews>
   <sheets>
     <sheet name="Python" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3676" uniqueCount="1870">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3786" uniqueCount="1971">
   <si>
     <t>Program NO</t>
   </si>
@@ -6023,6 +6023,336 @@
   </si>
   <si>
     <t>the object able to only call those method which are visible to that object</t>
+  </si>
+  <si>
+    <t>Use of super class to provide argument to base class and acces  the element from base calss</t>
+  </si>
+  <si>
+    <t>this Pointer in Jaava and how it works</t>
+  </si>
+  <si>
+    <t>if a calss contain the base derived calss can inherited  it and and base class contain characterstics then derived class provide the characterstics using super</t>
+  </si>
+  <si>
+    <t>methos of overloading in java</t>
+  </si>
+  <si>
+    <t>Cure of overloading gesture should be different</t>
+  </si>
+  <si>
+    <t>Dynamic memory alloacation in java</t>
+  </si>
+  <si>
+    <t>length prroperty In java of array</t>
+  </si>
+  <si>
+    <t>creating dynmaic 2d array in java</t>
+  </si>
+  <si>
+    <t>Jagged array in Java having number of rows are fixed but number of column are changed</t>
+  </si>
+  <si>
+    <t>printing jagged array</t>
+  </si>
+  <si>
+    <t>how exception occur during the exection of program</t>
+  </si>
+  <si>
+    <t>Exception is handled by using try and catch block and also used finally block</t>
+  </si>
+  <si>
+    <t>throws key word is used to resolve the exception that alaways happen generally used for checked exception checked exception that it will throw</t>
+  </si>
+  <si>
+    <t>issuue solved by using throws exception</t>
+  </si>
+  <si>
+    <t>Throwing userdefined exception by using try catch and by using or extending Exception class</t>
+  </si>
+  <si>
+    <t>Overriding in java oop but before undesrtand the concept of upcasting and Single level Inheritance and one redefination of any function</t>
+  </si>
+  <si>
+    <t>Understainding the concept of upcasting and downcasting 1. if small capacity of data poiting to large capacity of data then upcasting and it is allowed 2 . If large capacity of data ppointing to small capacity of data then it is down casting and it is not allowed because of pointer</t>
+  </si>
+  <si>
+    <t>Final In Java we can declare either function as a final or we can declare final as a class</t>
+  </si>
+  <si>
+    <t>Creating abstract class contain abstract method init so we can not create the object of that class but we can inherit it</t>
+  </si>
+  <si>
+    <t>Interfce in java  Interface is blue print of a class or a collection of a class</t>
+  </si>
+  <si>
+    <t>In java we can not do multiple level inheritance but by using interface we can perform multiple level inheritance</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>Interface</t>
+  </si>
+  <si>
+    <t>contain abstract as well as Concrete function</t>
+  </si>
+  <si>
+    <t>Contain only abstract function</t>
+  </si>
+  <si>
+    <t>Characaterstics are able to change</t>
+  </si>
+  <si>
+    <t>Characterstics are by default public ,static final</t>
+  </si>
+  <si>
+    <t>Behaviours are depends upon us</t>
+  </si>
+  <si>
+    <t>Behaviours are Bydefulat public and abstract</t>
+  </si>
+  <si>
+    <t>Can not Create object</t>
+  </si>
+  <si>
+    <t>can not create object</t>
+  </si>
+  <si>
+    <t>we can not write constructor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We can write construcotr </t>
+  </si>
+  <si>
+    <t>String in java Inbuilt String sobj = "Jay Ganesh.."; string is stored (Memory allocation in pool)in a string constant pool</t>
+  </si>
+  <si>
+    <t>String Consst ans String Literal</t>
+  </si>
+  <si>
+    <t>Getting hashcode of string</t>
+  </si>
+  <si>
+    <t>comparion address of string</t>
+  </si>
+  <si>
+    <t>Equals methos in java to comparison string</t>
+  </si>
+  <si>
+    <t>String Length method</t>
+  </si>
+  <si>
+    <t>Multithreading in  java Thread is a process which work parallel in execution in process there is one thread name main()</t>
+  </si>
+  <si>
+    <r>
+      <t>Creating Base class by using</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> extends Thread</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Creating Base Thread but by using interface but we have to use this syntsx Base </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">bobj = new Base();Thread tobj = new Thread(bobj);
+        </t>
+    </r>
+  </si>
+  <si>
+    <t>Adding join method to thread that will tell the main thread you will keepl alive till my wrok is completed</t>
+  </si>
+  <si>
+    <t>Adding Sleep Method to thread its reqiure try catch</t>
+  </si>
+  <si>
+    <t>Creating two thread but it work randomly when we call start();</t>
+  </si>
+  <si>
+    <t>creating two thread and could not say which will schedule first</t>
+  </si>
+  <si>
+    <t>Creating thread and call run method</t>
+  </si>
+  <si>
+    <t>Running Wait method</t>
+  </si>
+  <si>
+    <t>Object class in java is automatically inherited in all class that mmeans java will do Mulitple inheriance but ic can do to user</t>
+  </si>
+  <si>
+    <t>Finalize method from object class to call the destructor of a class</t>
+  </si>
+  <si>
+    <t>getClass() is tell Class Name of the object</t>
+  </si>
+  <si>
+    <t>hashcode() is similar like address in C and C++</t>
+  </si>
+  <si>
+    <t>toString() method in java is to Disply the charactertics of a class</t>
+  </si>
+  <si>
+    <t>Clone() method in java require exception handling of ClonenotfoundException or throws Exception</t>
+  </si>
+  <si>
+    <t>equlas()method in java but we have to check manuallly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">overiride() the equal </t>
+  </si>
+  <si>
+    <t>Number is Even or Not using If ans else statement without using function</t>
+  </si>
+  <si>
+    <t>Creating Function EvenorOdd in a same class but the function is static there is no need to create a object</t>
+  </si>
+  <si>
+    <t>Creating a new class and adding EvenorOdd() functon by creating a object we can call it</t>
+  </si>
+  <si>
+    <t>Calculate Ticket Price by using if else ladder</t>
+  </si>
+  <si>
+    <t>Adding filter to ticket Price</t>
+  </si>
+  <si>
+    <t>Sequence in java</t>
+  </si>
+  <si>
+    <t>Converintg Sequence in java</t>
+  </si>
+  <si>
+    <t>Adding Scanner Class for input</t>
+  </si>
+  <si>
+    <t>moved to function and by creating object calling a function</t>
+  </si>
+  <si>
+    <t>Reverse the loop</t>
+  </si>
+  <si>
+    <t>Adding multthread and making timer in java by using and reversing the loop</t>
+  </si>
+  <si>
+    <t>Checking Number is divisible by 3 and 5</t>
+  </si>
+  <si>
+    <t>Moving to function</t>
+  </si>
+  <si>
+    <t>Creating funcction that will display the factors of a number</t>
+  </si>
+  <si>
+    <t>Creating afunction that will return the sum of factor O(n)</t>
+  </si>
+  <si>
+    <t>Perfect() function created</t>
+  </si>
+  <si>
+    <t>Adding break condition if isum is greater than then the loop will break</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CheckPrime() Number by creating finction </t>
+  </si>
+  <si>
+    <t>modification in CheckPrime() function half of the loop</t>
+  </si>
+  <si>
+    <t>Do not return direct value because remainnig instruction remains in memory that will be exdcuted</t>
+  </si>
+  <si>
+    <t>by iCount we can aloso check number is prime or not if iCnt &lt; iNo  / 2 then number is not prime return false because number is divided</t>
+  </si>
+  <si>
+    <t>similarly by using converse of previous we can also write if (iCnt &gt;= (iNo/2) + 1 ) then return true because counter not divided any number else return false</t>
+  </si>
+  <si>
+    <t>While loop in java</t>
+  </si>
+  <si>
+    <t>do{} while(condition) loop in java</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reverising the while loop </t>
+  </si>
+  <si>
+    <t>Creating sequence the reverse of a number</t>
+  </si>
+  <si>
+    <t>by using previous sequence converting into while loop</t>
+  </si>
+  <si>
+    <t>Display the digit in reverse order by using function</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count digit function </t>
+  </si>
+  <si>
+    <t>Count EvenDigit function</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SumDigit function </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkpalindrome function </t>
+  </si>
+  <si>
+    <t>Array in java how to iniitalise array</t>
+  </si>
+  <si>
+    <t>CountOddDigit function</t>
+  </si>
+  <si>
+    <t>Taling input and output In java</t>
+  </si>
+  <si>
+    <t>initialisation of array in java</t>
+  </si>
+  <si>
+    <t>Callbyaddress in java</t>
+  </si>
+  <si>
+    <t>Summation of array</t>
+  </si>
+  <si>
+    <t>CountOfeven Number in  Array</t>
+  </si>
+  <si>
+    <t>SumOfeven numbser in Array</t>
+  </si>
+  <si>
+    <t>CountOfOdd number in Array</t>
+  </si>
+  <si>
+    <t>SumOfEven number in Array</t>
+  </si>
+  <si>
+    <t>String in jav</t>
+  </si>
+  <si>
+    <t>in java string slicing not allowed</t>
+  </si>
+  <si>
+    <t>Instead of [] this java provide charAt() mehod</t>
   </si>
 </sst>
 </file>
@@ -6086,7 +6416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -6100,6 +6430,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15707,12 +16038,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4D2A8D0-F6AB-4F67-AFD3-1E5715634D73}">
-  <dimension ref="A1:C432"/>
+  <dimension ref="A1:G432"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="103.33203125" customWidth="1"/>
+    <col min="3" max="3" width="219.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.3">
@@ -16159,6 +16492,9 @@
       <c r="B41" t="s">
         <v>1722</v>
       </c>
+      <c r="C41" t="s">
+        <v>1871</v>
+      </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
@@ -16167,6 +16503,9 @@
       <c r="B42" t="s">
         <v>1722</v>
       </c>
+      <c r="C42" t="s">
+        <v>1870</v>
+      </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
@@ -16175,6 +16514,9 @@
       <c r="B43" t="s">
         <v>1722</v>
       </c>
+      <c r="C43" t="s">
+        <v>1872</v>
+      </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
@@ -16183,6 +16525,9 @@
       <c r="B44" t="s">
         <v>1722</v>
       </c>
+      <c r="C44" t="s">
+        <v>1873</v>
+      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
@@ -16191,6 +16536,9 @@
       <c r="B45" t="s">
         <v>1722</v>
       </c>
+      <c r="C45" t="s">
+        <v>1874</v>
+      </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
@@ -16199,6 +16547,9 @@
       <c r="B46" t="s">
         <v>1722</v>
       </c>
+      <c r="C46" t="s">
+        <v>1875</v>
+      </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
@@ -16207,6 +16558,9 @@
       <c r="B47" t="s">
         <v>1722</v>
       </c>
+      <c r="C47" t="s">
+        <v>1876</v>
+      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
@@ -16215,325 +16569,505 @@
       <c r="B48" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C48" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>88</v>
       </c>
       <c r="B49" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C49" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>89</v>
       </c>
       <c r="B50" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C50" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>90</v>
       </c>
       <c r="B51" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C51" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B52" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B53" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B54" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B55" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B56" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B57" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B58" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B59" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B60" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>100</v>
       </c>
       <c r="B61" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="F61" s="5" t="s">
+        <v>1891</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>101</v>
       </c>
       <c r="B62" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="F62" s="5" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>102</v>
       </c>
       <c r="B63" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="F63" s="5" t="s">
+        <v>1895</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>103</v>
       </c>
       <c r="B64" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C64" t="s">
+        <v>1888</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>1897</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>104</v>
       </c>
       <c r="B65" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C65" t="s">
+        <v>1889</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>105</v>
       </c>
       <c r="B66" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C66" t="s">
+        <v>1890</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>106</v>
       </c>
       <c r="B67" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C67" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>107</v>
       </c>
       <c r="B68" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C68" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>108</v>
       </c>
       <c r="B69" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C69" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>109</v>
       </c>
       <c r="B70" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C70" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>110</v>
       </c>
       <c r="B71" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C71" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>111</v>
       </c>
       <c r="B72" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C72" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>112</v>
       </c>
       <c r="B73" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C73" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>113</v>
       </c>
       <c r="B74" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C74" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>114</v>
       </c>
       <c r="B75" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C75" s="3" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>115</v>
       </c>
       <c r="B76" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C76" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>116</v>
       </c>
       <c r="B77" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C77" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>117</v>
       </c>
       <c r="B78" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C78" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>118</v>
       </c>
       <c r="B79" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C79" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>119</v>
       </c>
       <c r="B80" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C80" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>120</v>
       </c>
       <c r="B81" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C81" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>121</v>
       </c>
       <c r="B82" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C82" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>122</v>
       </c>
       <c r="B83" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C83" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>123</v>
       </c>
       <c r="B84" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C84" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>124</v>
       </c>
       <c r="B85" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C85" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>125</v>
       </c>
       <c r="B86" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C86" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>126</v>
       </c>
       <c r="B87" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C87" t="s">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>127</v>
       </c>
       <c r="B88" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C88" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>128</v>
       </c>
       <c r="B89" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C89" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>129</v>
       </c>
       <c r="B90" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C90" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>130</v>
       </c>
       <c r="B91" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C91" t="s">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>131</v>
       </c>
@@ -16541,111 +17075,150 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>132</v>
       </c>
       <c r="B93" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C93" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>133</v>
       </c>
       <c r="B94" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C94" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>134</v>
       </c>
       <c r="B95" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C95" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>135</v>
       </c>
       <c r="B96" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C96" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>136</v>
       </c>
       <c r="B97" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C97" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>137</v>
       </c>
       <c r="B98" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C98" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>138</v>
       </c>
       <c r="B99" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C99" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>139</v>
       </c>
       <c r="B100" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C100" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>140</v>
       </c>
       <c r="B101" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C101" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>141</v>
       </c>
       <c r="B102" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C102" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>142</v>
       </c>
       <c r="B103" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C103" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>143</v>
       </c>
       <c r="B104" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C104" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>144</v>
       </c>
       <c r="B105" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C105" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>145</v>
       </c>
@@ -16653,23 +17226,29 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>146</v>
       </c>
       <c r="B107" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C107" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>147</v>
       </c>
       <c r="B108" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C108" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>148</v>
       </c>
@@ -16677,7 +17256,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>149</v>
       </c>
@@ -16685,7 +17264,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>150</v>
       </c>
@@ -16693,7 +17272,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>151</v>
       </c>
@@ -16701,7 +17280,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>152</v>
       </c>
@@ -16709,7 +17288,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>153</v>
       </c>
@@ -16717,7 +17296,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>154</v>
       </c>
@@ -16725,7 +17304,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>155</v>
       </c>
@@ -16733,7 +17312,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>156</v>
       </c>
@@ -16741,7 +17320,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>157</v>
       </c>
@@ -16749,7 +17328,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>158</v>
       </c>
@@ -16757,7 +17336,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>159</v>
       </c>
@@ -16765,207 +17344,282 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>160</v>
       </c>
       <c r="B121" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C121" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>161</v>
       </c>
       <c r="B122" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C122" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>162</v>
       </c>
       <c r="B123" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C123" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>163</v>
       </c>
       <c r="B124" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C124" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>164</v>
       </c>
       <c r="B125" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C125" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>165</v>
       </c>
       <c r="B126" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C126" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>166</v>
       </c>
       <c r="B127" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C127" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>167</v>
       </c>
       <c r="B128" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C128" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>168</v>
       </c>
       <c r="B129" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C129" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>169</v>
       </c>
       <c r="B130" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C130" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>170</v>
       </c>
       <c r="B131" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C131" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>171</v>
       </c>
       <c r="B132" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C132" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>172</v>
       </c>
       <c r="B133" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C133" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>173</v>
       </c>
       <c r="B134" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C134" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>174</v>
       </c>
       <c r="B135" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C135" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>175</v>
       </c>
       <c r="B136" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C136" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>176</v>
       </c>
       <c r="B137" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C137" t="s">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>177</v>
       </c>
       <c r="B138" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C138" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>178</v>
       </c>
       <c r="B139" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C139" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>179</v>
       </c>
       <c r="B140" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C140" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>180</v>
       </c>
       <c r="B141" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C141" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>181</v>
       </c>
       <c r="B142" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C142" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>182</v>
       </c>
       <c r="B143" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C143" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>183</v>
       </c>
       <c r="B144" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C144" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>184</v>
       </c>
       <c r="B145" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C145" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>185</v>
       </c>
@@ -16973,7 +17627,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>186</v>
       </c>
@@ -16981,7 +17635,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>187</v>
       </c>
@@ -16989,7 +17643,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>188</v>
       </c>
@@ -16997,7 +17651,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>189</v>
       </c>
@@ -17005,7 +17659,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>190</v>
       </c>
@@ -17013,7 +17667,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>191</v>
       </c>
@@ -17021,7 +17675,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>192</v>
       </c>
@@ -17029,7 +17683,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>193</v>
       </c>
@@ -17037,7 +17691,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>194</v>
       </c>
@@ -17045,7 +17699,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>195</v>
       </c>
@@ -17053,7 +17707,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>196</v>
       </c>
@@ -17061,7 +17715,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>197</v>
       </c>
@@ -17069,7 +17723,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>198</v>
       </c>
@@ -17077,7 +17731,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>199</v>
       </c>
@@ -17341,7 +17995,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>232</v>
       </c>
@@ -17349,7 +18003,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>233</v>
       </c>
@@ -17357,7 +18011,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>234</v>
       </c>
@@ -17365,7 +18019,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>235</v>
       </c>
@@ -17373,7 +18027,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>236</v>
       </c>
@@ -17381,7 +18035,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>237</v>
       </c>
@@ -17389,7 +18043,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>238</v>
       </c>
@@ -17397,7 +18051,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>239</v>
       </c>
@@ -17405,31 +18059,40 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>1490</v>
       </c>
       <c r="B201" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C201" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>1491</v>
       </c>
       <c r="B202" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C202" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>1492</v>
       </c>
       <c r="B203" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C203" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>1493</v>
       </c>
@@ -17437,7 +18100,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>1494</v>
       </c>
@@ -17445,7 +18108,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>1495</v>
       </c>
@@ -17453,7 +18116,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>1496</v>
       </c>
@@ -17461,7 +18124,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>1497</v>
       </c>
